--- a/public/files/DATA/CHR_data.xlsx
+++ b/public/files/DATA/CHR_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280456CB-AB19-420D-B929-7D15FD912089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E63DEB-B256-4249-8429-9642337F505F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2385" yWindow="990" windowWidth="27990" windowHeight="14415" activeTab="3" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
+    <workbookView xWindow="1170" yWindow="255" windowWidth="20640" windowHeight="14895" activeTab="5" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
   </bookViews>
   <sheets>
     <sheet name="共通ﾃﾞｰﾀ" sheetId="9" r:id="rId1"/>

--- a/public/files/DATA/CHR_data.xlsx
+++ b/public/files/DATA/CHR_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E63DEB-B256-4249-8429-9642337F505F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17C19D9-06B5-4578-9268-6A3CC02F7B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="255" windowWidth="20640" windowHeight="14895" activeTab="5" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
+    <workbookView xWindow="1380" yWindow="585" windowWidth="26205" windowHeight="14895" firstSheet="1" activeTab="7" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
   </bookViews>
   <sheets>
     <sheet name="共通ﾃﾞｰﾀ" sheetId="9" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="12蒼樹" sheetId="6" r:id="rId5"/>
     <sheet name="9紅華" sheetId="7" r:id="rId6"/>
     <sheet name="4黄蘭" sheetId="8" r:id="rId7"/>
+    <sheet name="9白蓮" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="355">
   <si>
     <t>李乃果</t>
     <rPh sb="0" eb="1">
@@ -4990,6 +4991,314 @@
   </si>
   <si>
     <t>・戦闘中ダメージ10ごとに精神力を1失う設定だが、さらに1多く減る。</t>
+  </si>
+  <si>
+    <t>白蓮</t>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ハス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黄蘭は遠距離からはデバフ性能のあるレーザーを撃つ</t>
+    <rPh sb="0" eb="2">
+      <t>オウラ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>エンキョリ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セイノウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近距離では敵を押し返すバリアを張る</t>
+    <rPh sb="0" eb="3">
+      <t>キンキョリ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>隠者</t>
+    <rPh sb="0" eb="2">
+      <t>インジャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>011001.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右向き立ち絵</t>
+    <rPh sb="0" eb="2">
+      <t>ミギム</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>011001b.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>011002.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>011002b.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レーザー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>射程内の敵を弾き飛ばす。</t>
+    <rPh sb="0" eb="2">
+      <t>シャテイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バリア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージを1/3減衰しながら貫通。敵の弾丸を消す。</t>
+    <rPh sb="8" eb="10">
+      <t>ゲンスイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンツウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>発射時は直径0.5mだが直径2mまで広がりゆっくり前進する。ダメージを1/3減衰しながら貫通。敵の弾丸を消す。</t>
+    <rPh sb="0" eb="3">
+      <t>ハッシャジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チョッケイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>チョッケイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ゼンシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブレ(目標角度からの拡散)</t>
+    <rPh sb="3" eb="5">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カクサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8秒に1回、前方に秒速0.5mで進む直径1mのバリア弾を形成する。攻撃力0 ノックバック40 敵弾丸に接触すると弾丸を消す。弾丸への耐久力はWLV個分。それだけの弾丸を受けるか、敵に接触すると消える。</t>
+    <rPh sb="1" eb="2">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゼンポウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ビョウソク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>チョッケイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ケイセイ</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>セッショク</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>タイキュウ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>リョク</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>セッショク</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前方に秒速2mで進む直径1mのバリア弾を形成する。攻撃力0 ノックバック40 敵弾丸に接触すると弾丸を消す。15m進むと直径8mに拡大して破裂し、範囲内に基本攻撃力の(100+10*WLV)％のダメージ。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンポウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ビョウソク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>チョッケイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケイセイ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>セッショク</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>チョッケイ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>カクダイ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ハレツ</t>
+    </rPh>
+    <rPh sb="73" eb="76">
+      <t>ハンイナイ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="79" eb="82">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11003.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ﾚｰｻﾞｰ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11003b.png</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -5130,7 +5439,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5159,6 +5468,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -15368,4 +15680,1623 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1462EC-F2B4-4748-B5F2-4C03CEBAE5D3}">
+  <dimension ref="A1:AA90"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>750</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1250</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>336</v>
+      </c>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>338</v>
+      </c>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>339</v>
+      </c>
+      <c r="D13" t="s">
+        <v>340</v>
+      </c>
+      <c r="E13" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>342</v>
+      </c>
+      <c r="C14" t="s">
+        <v>343</v>
+      </c>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>352</v>
+      </c>
+      <c r="C15" t="s">
+        <v>353</v>
+      </c>
+      <c r="E15" t="s">
+        <v>354</v>
+      </c>
+      <c r="F15" t="s">
+        <v>346</v>
+      </c>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
+        <v>135</v>
+      </c>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>134</v>
+      </c>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>136</v>
+      </c>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" t="s">
+        <v>126</v>
+      </c>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>344</v>
+      </c>
+      <c r="D22">
+        <v>50</v>
+      </c>
+      <c r="E22">
+        <v>0.5</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>45</v>
+      </c>
+      <c r="H22">
+        <v>19</v>
+      </c>
+      <c r="I22">
+        <v>5</v>
+      </c>
+      <c r="J22" t="s">
+        <v>347</v>
+      </c>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>16</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23" t="s">
+        <v>24</v>
+      </c>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" t="s">
+        <v>21</v>
+      </c>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="10"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
+        <v>346</v>
+      </c>
+      <c r="D28">
+        <v>50</v>
+      </c>
+      <c r="E28">
+        <v>0.3</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>6</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
+      </c>
+      <c r="J28" t="s">
+        <v>348</v>
+      </c>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="10"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29">
+        <v>15</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>30</v>
+      </c>
+      <c r="H29">
+        <v>1.5</v>
+      </c>
+      <c r="I29">
+        <v>40</v>
+      </c>
+      <c r="J29" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B31" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B32" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
+      <c r="V33" s="10"/>
+      <c r="W33" s="10"/>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="10"/>
+      <c r="V34" s="10"/>
+      <c r="W34" s="10"/>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s">
+        <v>349</v>
+      </c>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10"/>
+      <c r="V35" s="10"/>
+      <c r="W35" s="10"/>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <v>1</v>
+      </c>
+      <c r="B36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" t="s">
+        <v>344</v>
+      </c>
+      <c r="D36">
+        <v>50</v>
+      </c>
+      <c r="E36">
+        <v>0.1</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>45</v>
+      </c>
+      <c r="H36">
+        <v>19</v>
+      </c>
+      <c r="I36">
+        <v>5</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>16</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <v>2</v>
+      </c>
+      <c r="B39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
+        <v>344</v>
+      </c>
+      <c r="D39">
+        <v>30</v>
+      </c>
+      <c r="E39">
+        <v>0.1</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39">
+        <v>45</v>
+      </c>
+      <c r="H39">
+        <v>19</v>
+      </c>
+      <c r="I39">
+        <v>5</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <v>2</v>
+      </c>
+      <c r="B40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>16</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
+        <v>344</v>
+      </c>
+      <c r="D42">
+        <v>24</v>
+      </c>
+      <c r="E42">
+        <v>0.1</v>
+      </c>
+      <c r="F42">
+        <v>3</v>
+      </c>
+      <c r="G42">
+        <v>45</v>
+      </c>
+      <c r="H42">
+        <v>19</v>
+      </c>
+      <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A43">
+        <v>3</v>
+      </c>
+      <c r="B43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>16</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" t="s">
+        <v>344</v>
+      </c>
+      <c r="D45">
+        <v>20</v>
+      </c>
+      <c r="E45">
+        <v>0.1</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
+      </c>
+      <c r="G45">
+        <v>45</v>
+      </c>
+      <c r="H45">
+        <v>19</v>
+      </c>
+      <c r="I45">
+        <v>5</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A46">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>16</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <v>5</v>
+      </c>
+      <c r="B48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" t="s">
+        <v>344</v>
+      </c>
+      <c r="D48">
+        <v>18</v>
+      </c>
+      <c r="E48">
+        <v>0.1</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+      <c r="G48">
+        <v>45</v>
+      </c>
+      <c r="H48">
+        <v>19</v>
+      </c>
+      <c r="I48">
+        <v>5</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A49">
+        <v>5</v>
+      </c>
+      <c r="B49" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>16</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A51">
+        <v>6</v>
+      </c>
+      <c r="B51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" t="s">
+        <v>344</v>
+      </c>
+      <c r="D51">
+        <v>17</v>
+      </c>
+      <c r="E51">
+        <v>0.1</v>
+      </c>
+      <c r="F51">
+        <v>6</v>
+      </c>
+      <c r="G51">
+        <v>45</v>
+      </c>
+      <c r="H51">
+        <v>19</v>
+      </c>
+      <c r="I51">
+        <v>5</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A52">
+        <v>6</v>
+      </c>
+      <c r="B52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>16</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A54">
+        <v>7</v>
+      </c>
+      <c r="B54" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" t="s">
+        <v>344</v>
+      </c>
+      <c r="D54">
+        <v>17</v>
+      </c>
+      <c r="E54">
+        <v>0.1</v>
+      </c>
+      <c r="F54">
+        <v>7</v>
+      </c>
+      <c r="G54">
+        <v>45</v>
+      </c>
+      <c r="H54">
+        <v>19</v>
+      </c>
+      <c r="I54">
+        <v>5</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A55">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>16</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" t="s">
+        <v>174</v>
+      </c>
+      <c r="J57" t="s">
+        <v>21</v>
+      </c>
+      <c r="K57" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A58">
+        <v>1</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" t="s">
+        <v>346</v>
+      </c>
+      <c r="D58">
+        <v>50</v>
+      </c>
+      <c r="E58">
+        <v>0.3</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>6</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>10</v>
+      </c>
+      <c r="K58">
+        <v>6</v>
+      </c>
+      <c r="L58" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A59">
+        <v>1</v>
+      </c>
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" t="s">
+        <v>27</v>
+      </c>
+      <c r="D59">
+        <v>15</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>30</v>
+      </c>
+      <c r="H59">
+        <v>2</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+      <c r="J59">
+        <v>40</v>
+      </c>
+      <c r="K59">
+        <v>1.5</v>
+      </c>
+      <c r="L59" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A61">
+        <v>2</v>
+      </c>
+      <c r="B61" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" t="s">
+        <v>346</v>
+      </c>
+      <c r="D61">
+        <v>50</v>
+      </c>
+      <c r="E61">
+        <v>0.3</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>6</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>10</v>
+      </c>
+      <c r="K61">
+        <v>6</v>
+      </c>
+      <c r="L61" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A62">
+        <v>2</v>
+      </c>
+      <c r="B62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62">
+        <v>15</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>30</v>
+      </c>
+      <c r="H62">
+        <v>2</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
+        <v>40</v>
+      </c>
+      <c r="K62">
+        <v>1.5</v>
+      </c>
+      <c r="L62" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A64">
+        <v>3</v>
+      </c>
+      <c r="B64" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" t="s">
+        <v>346</v>
+      </c>
+      <c r="D64">
+        <v>50</v>
+      </c>
+      <c r="E64">
+        <v>0.3</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>6</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>10</v>
+      </c>
+      <c r="K64">
+        <v>6</v>
+      </c>
+      <c r="L64" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A65">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65">
+        <v>15</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>30</v>
+      </c>
+      <c r="H65">
+        <v>2</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>40</v>
+      </c>
+      <c r="K65">
+        <v>1.5</v>
+      </c>
+      <c r="L65" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A67">
+        <v>4</v>
+      </c>
+      <c r="B67" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" t="s">
+        <v>346</v>
+      </c>
+      <c r="D67">
+        <v>50</v>
+      </c>
+      <c r="E67">
+        <v>0.3</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>6</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>10</v>
+      </c>
+      <c r="K67">
+        <v>6</v>
+      </c>
+      <c r="L67" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A68">
+        <v>4</v>
+      </c>
+      <c r="B68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68">
+        <v>15</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>30</v>
+      </c>
+      <c r="H68">
+        <v>2</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>40</v>
+      </c>
+      <c r="K68">
+        <v>1.5</v>
+      </c>
+      <c r="L68" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A70">
+        <v>5</v>
+      </c>
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70" t="s">
+        <v>346</v>
+      </c>
+      <c r="D70">
+        <v>50</v>
+      </c>
+      <c r="E70">
+        <v>0.3</v>
+      </c>
+      <c r="F70">
+        <v>2</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>6</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>10</v>
+      </c>
+      <c r="K70">
+        <v>6</v>
+      </c>
+      <c r="L70" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A71">
+        <v>5</v>
+      </c>
+      <c r="B71" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71" t="s">
+        <v>27</v>
+      </c>
+      <c r="D71">
+        <v>15</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>30</v>
+      </c>
+      <c r="H71">
+        <v>2</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71">
+        <v>40</v>
+      </c>
+      <c r="K71">
+        <v>1.5</v>
+      </c>
+      <c r="L71" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A73">
+        <v>6</v>
+      </c>
+      <c r="B73" t="s">
+        <v>25</v>
+      </c>
+      <c r="C73" t="s">
+        <v>346</v>
+      </c>
+      <c r="D73">
+        <v>50</v>
+      </c>
+      <c r="E73">
+        <v>0.3</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>6</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>10</v>
+      </c>
+      <c r="K73">
+        <v>6</v>
+      </c>
+      <c r="L73" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A74">
+        <v>6</v>
+      </c>
+      <c r="B74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C74" t="s">
+        <v>27</v>
+      </c>
+      <c r="D74">
+        <v>15</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>30</v>
+      </c>
+      <c r="H74">
+        <v>2</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <v>40</v>
+      </c>
+      <c r="K74">
+        <v>1.5</v>
+      </c>
+      <c r="L74" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A76">
+        <v>7</v>
+      </c>
+      <c r="B76" t="s">
+        <v>25</v>
+      </c>
+      <c r="C76" t="s">
+        <v>346</v>
+      </c>
+      <c r="D76">
+        <v>50</v>
+      </c>
+      <c r="E76">
+        <v>0.3</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>6</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>10</v>
+      </c>
+      <c r="K76">
+        <v>6</v>
+      </c>
+      <c r="L76" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A77">
+        <v>7</v>
+      </c>
+      <c r="B77" t="s">
+        <v>25</v>
+      </c>
+      <c r="C77" t="s">
+        <v>27</v>
+      </c>
+      <c r="D77">
+        <v>15</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77">
+        <v>30</v>
+      </c>
+      <c r="H77">
+        <v>2</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>40</v>
+      </c>
+      <c r="K77">
+        <v>1.5</v>
+      </c>
+      <c r="L77" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A88" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>351</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/public/files/DATA/CHR_data.xlsx
+++ b/public/files/DATA/CHR_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17C19D9-06B5-4578-9268-6A3CC02F7B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21451D65-BCCD-4C59-AF52-B256DEE68CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="585" windowWidth="26205" windowHeight="14895" firstSheet="1" activeTab="7" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="359">
   <si>
     <t>李乃果</t>
     <rPh sb="0" eb="1">
@@ -5298,6 +5298,28 @@
   </si>
   <si>
     <t>11003b.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遭遇ヘクス</t>
+    <rPh sb="0" eb="2">
+      <t>ソウグウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>池袋</t>
+    <rPh sb="0" eb="2">
+      <t>イケブクロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポートレート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>011p.jpg</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -15770,6 +15792,12 @@
       <c r="AA9" s="9"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>355</v>
+      </c>
+      <c r="B10" t="s">
+        <v>356</v>
+      </c>
       <c r="Z10" s="9"/>
       <c r="AA10" s="9"/>
     </row>
@@ -15808,6 +15836,12 @@
       </c>
       <c r="E13" t="s">
         <v>341</v>
+      </c>
+      <c r="G13" t="s">
+        <v>357</v>
+      </c>
+      <c r="H13" t="s">
+        <v>358</v>
       </c>
       <c r="Z13" s="9"/>
       <c r="AA13" s="9"/>

--- a/public/files/DATA/CHR_data.xlsx
+++ b/public/files/DATA/CHR_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21451D65-BCCD-4C59-AF52-B256DEE68CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7608488-A1ED-4C1F-9C74-F215BA90F9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="585" windowWidth="26205" windowHeight="14895" firstSheet="1" activeTab="7" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
+    <workbookView xWindow="2340" yWindow="1305" windowWidth="26205" windowHeight="14895" firstSheet="1" activeTab="7" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
   </bookViews>
   <sheets>
     <sheet name="共通ﾃﾞｰﾀ" sheetId="9" r:id="rId1"/>
@@ -5461,7 +5461,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5490,9 +5490,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -15856,11 +15853,6 @@
       <c r="C14" t="s">
         <v>343</v>
       </c>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="9"/>
     </row>
@@ -15880,63 +15872,31 @@
       <c r="F15" t="s">
         <v>346</v>
       </c>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
         <v>135</v>
       </c>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
         <v>134</v>
       </c>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
         <v>136</v>
       </c>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>125</v>
       </c>
       <c r="B20" t="s">
         <v>126</v>
       </c>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10"/>
-      <c r="T20" s="10"/>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -15961,13 +15921,8 @@
       <c r="I21" t="s">
         <v>21</v>
       </c>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10"/>
-      <c r="S21" s="10"/>
-      <c r="T21" s="10"/>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>1</v>
       </c>
@@ -15998,13 +15953,8 @@
       <c r="J22" t="s">
         <v>347</v>
       </c>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="10"/>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>1</v>
       </c>
@@ -16035,34 +15985,8 @@
       <c r="J23" t="s">
         <v>24</v>
       </c>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10"/>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
-      <c r="S24" s="10"/>
-      <c r="T24" s="10"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="10"/>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="10"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -16087,13 +16011,8 @@
       <c r="I27" t="s">
         <v>21</v>
       </c>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="10"/>
-      <c r="S27" s="10"/>
-      <c r="T27" s="10"/>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>1</v>
       </c>
@@ -16124,13 +16043,8 @@
       <c r="J28" t="s">
         <v>348</v>
       </c>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="10"/>
-      <c r="S28" s="10"/>
-      <c r="T28" s="10"/>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>1</v>
       </c>
@@ -16162,33 +16076,17 @@
         <v>345</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B31" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B32" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="R33" s="10"/>
-      <c r="S33" s="10"/>
-      <c r="T33" s="10"/>
-      <c r="U33" s="10"/>
-      <c r="V33" s="10"/>
-      <c r="W33" s="10"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="R34" s="10"/>
-      <c r="S34" s="10"/>
-      <c r="T34" s="10"/>
-      <c r="U34" s="10"/>
-      <c r="V34" s="10"/>
-      <c r="W34" s="10"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -16216,14 +16114,8 @@
       <c r="J35" t="s">
         <v>349</v>
       </c>
-      <c r="R35" s="10"/>
-      <c r="S35" s="10"/>
-      <c r="T35" s="10"/>
-      <c r="U35" s="10"/>
-      <c r="V35" s="10"/>
-      <c r="W35" s="10"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>1</v>
       </c>
@@ -16258,7 +16150,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>1</v>
       </c>
@@ -16293,7 +16185,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>2</v>
       </c>
@@ -16328,7 +16220,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>2</v>
       </c>
@@ -16363,7 +16255,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>3</v>
       </c>
@@ -16398,7 +16290,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>3</v>
       </c>
@@ -16433,7 +16325,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>4</v>
       </c>
@@ -16468,7 +16360,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>4</v>
       </c>
@@ -16503,7 +16395,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>5</v>
       </c>
@@ -16756,7 +16648,7 @@
         <v>346</v>
       </c>
       <c r="D58">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E58">
         <v>0.3</v>
@@ -16832,13 +16724,13 @@
         <v>346</v>
       </c>
       <c r="D61">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E61">
         <v>0.3</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -16908,13 +16800,13 @@
         <v>346</v>
       </c>
       <c r="D64">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E64">
         <v>0.3</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -16984,13 +16876,13 @@
         <v>346</v>
       </c>
       <c r="D67">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E67">
         <v>0.3</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -17060,13 +16952,13 @@
         <v>346</v>
       </c>
       <c r="D70">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="E70">
         <v>0.3</v>
       </c>
       <c r="F70">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -17136,13 +17028,13 @@
         <v>346</v>
       </c>
       <c r="D73">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E73">
         <v>0.3</v>
       </c>
       <c r="F73">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -17212,13 +17104,13 @@
         <v>346</v>
       </c>
       <c r="D76">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E76">
         <v>0.3</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G76">
         <v>1</v>

--- a/public/files/DATA/CHR_data.xlsx
+++ b/public/files/DATA/CHR_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7608488-A1ED-4C1F-9C74-F215BA90F9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F48FB48-19C5-417B-AAA8-5120190DF232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1305" windowWidth="26205" windowHeight="14895" firstSheet="1" activeTab="7" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
+    <workbookView xWindow="1380" yWindow="585" windowWidth="26205" windowHeight="14895" firstSheet="1" activeTab="7" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
   </bookViews>
   <sheets>
     <sheet name="共通ﾃﾞｰﾀ" sheetId="9" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="360">
   <si>
     <t>李乃果</t>
     <rPh sb="0" eb="1">
@@ -5321,13 +5321,16 @@
   <si>
     <t>011p.jpg</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進む距離は15m？にしてたと思うけど8mとして。その爆発は5秒+（WLV/2）秒持続し、敵にダメージを与え続け(攻撃力の10%+WLV％)、弾丸を吸収し続ける。　</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5342,6 +5345,11 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5461,7 +5469,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5490,6 +5498,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -15703,7 +15714,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1462EC-F2B4-4748-B5F2-4C03CEBAE5D3}">
-  <dimension ref="A1:AA90"/>
+  <dimension ref="A1:AA91"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.4">
@@ -17218,6 +17229,11 @@
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
         <v>351</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A91" s="10" t="s">
+        <v>359</v>
       </c>
     </row>
   </sheetData>

--- a/public/files/DATA/CHR_data.xlsx
+++ b/public/files/DATA/CHR_data.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F48FB48-19C5-417B-AAA8-5120190DF232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63841D2-380C-4CDD-AD97-8888C84354F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="585" windowWidth="26205" windowHeight="14895" firstSheet="1" activeTab="7" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
+    <workbookView xWindow="855" yWindow="225" windowWidth="26205" windowHeight="14850" activeTab="10" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
   </bookViews>
   <sheets>
-    <sheet name="共通ﾃﾞｰﾀ" sheetId="9" r:id="rId1"/>
-    <sheet name="メイン進行ルーチン" sheetId="10" r:id="rId2"/>
-    <sheet name="10紫苑" sheetId="4" r:id="rId3"/>
-    <sheet name="15李乃果data" sheetId="2" r:id="rId4"/>
-    <sheet name="12蒼樹" sheetId="6" r:id="rId5"/>
-    <sheet name="9紅華" sheetId="7" r:id="rId6"/>
-    <sheet name="4黄蘭" sheetId="8" r:id="rId7"/>
-    <sheet name="9白蓮" sheetId="11" r:id="rId8"/>
+    <sheet name="tarot" sheetId="15" r:id="rId1"/>
+    <sheet name="共通ﾃﾞｰﾀ" sheetId="9" r:id="rId2"/>
+    <sheet name="メイン進行ルーチン" sheetId="10" r:id="rId3"/>
+    <sheet name="10紫苑" sheetId="4" r:id="rId4"/>
+    <sheet name="15李乃果data" sheetId="2" r:id="rId5"/>
+    <sheet name="12蒼樹" sheetId="6" r:id="rId6"/>
+    <sheet name="9紅華" sheetId="7" r:id="rId7"/>
+    <sheet name="4黄蘭" sheetId="8" r:id="rId8"/>
+    <sheet name="9白蓮" sheetId="11" r:id="rId9"/>
+    <sheet name="0ななよ" sheetId="13" r:id="rId10"/>
+    <sheet name="4ノア" sheetId="14" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="506">
   <si>
     <t>李乃果</t>
     <rPh sb="0" eb="1">
@@ -5324,13 +5327,1971 @@
   </si>
   <si>
     <t>進む距離は15m？にしてたと思うけど8mとして。その爆発は5秒+（WLV/2）秒持続し、敵にダメージを与え続け(攻撃力の10%+WLV％)、弾丸を吸収し続ける。　</t>
+  </si>
+  <si>
+    <t>愚者</t>
+    <rPh sb="0" eb="2">
+      <t>グシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死に顔</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>evx007.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紅華</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ななよ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ななよは遠距離からは三鈷杵を投げつける。</t>
+    <rPh sb="10" eb="13">
+      <t>サンコショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>007001.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>007001b.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>007002.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>007002b.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>007003.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三鈷杵投げ</t>
+    <rPh sb="0" eb="3">
+      <t>サンコショ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三鈷杵ブーメラン</t>
+    <rPh sb="0" eb="3">
+      <t>サンコショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パンチorリロード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上記の場合、(三鈷杵ブーメラン→0.4秒)後、ターゲットがまだ2m以内にいればパンチを発動する。</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>サンコショ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ハツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ターゲットがいない場合、リロード時間だけをうけてフリーの状態に戻る</t>
+    <rPh sb="9" eb="11">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵を貫通する。射程まで飛んで戻ってくる。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンツウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シャテイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>狙った敵に向かい、キャラクタから1.5mの地点を中心に三鈷杵が円を描いて飛ぶ。貫通100%</t>
+    <rPh sb="0" eb="1">
+      <t>ネラ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>チテン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>サンコショ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>エガ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カンツウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三鈷杵が一番耐久力のある敵に向かって秒速35mで15m進む。全貫通。攻撃力50+10*WLV</t>
+    <rPh sb="0" eb="3">
+      <t>サンコショ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>タイキュウリョク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ビョウソク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カンツウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0.3秒止まり、その場所からまた一番耐久力のある敵に向かって秒速35mで10m進む。4回行ったあと最後はななよに向かって戻り、ななよに接触すると消える。。</t>
+    <rPh sb="3" eb="4">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>セッショク</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12秒に1回、自身と、自身に隣り合ったレーンのメンバー2人の属性防御力、属性デバフ抵抗を30下げる。(ダメージを減少する)。3+wlv/2秒間維持される</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>トナ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>テイコウ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ビョウカン</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>イジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12秒に1回、自身と、自身に隣り合ったレーンのメンバー2人の属性防御力、属性デバフ抵抗を30下げる。(ダメージを減少する)。3+wlv/2秒間維持される</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>テイコウ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ビョウカン</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>イジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>管理番号</t>
+    <rPh sb="0" eb="4">
+      <t>カンリバンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>和名</t>
+    <rPh sb="0" eb="2">
+      <t>ワメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登場シナリオ</t>
+    <rPh sb="0" eb="2">
+      <t>トウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正位置</t>
+    <rPh sb="0" eb="3">
+      <t>セイイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>逆位置</t>
+    <rPh sb="0" eb="3">
+      <t>ギャクイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(主)ななよとノアの呪文</t>
+    <rPh sb="10" eb="12">
+      <t>ジュモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>探索時の獲得報酬のレア取得率が上がる</t>
+    <rPh sb="0" eb="3">
+      <t>タンサクジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホウシュウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>シュトクリツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前衛配置のキャラクタの攻撃力が20％UPし、被ダメージが20％増し(端数切上げ)になる</t>
+    <rPh sb="31" eb="32">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ハスウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>キリア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔術師</t>
+    <rPh sb="0" eb="3">
+      <t>マジュツシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アリス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ななよとノアの呪文</t>
+    <rPh sb="7" eb="9">
+      <t>ジュモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全員のリロード速度が10%短縮される</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルの精神力消費が倍になり、威力や効果、継続時間も2倍になる</t>
+    <rPh sb="4" eb="7">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>ケイゾクジカン</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>女教皇</t>
+    <rPh sb="0" eb="1">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>キョウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しおり</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>味方全員の攻撃の命中率が20%上がる</t>
+    <rPh sb="0" eb="2">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>味方全員の命中率、攻撃力が10%上がる</t>
+    <rPh sb="0" eb="4">
+      <t>ミカタゼンイン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黄蘭</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マギアピルグリム1章</t>
+    <rPh sb="9" eb="10">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>味方全員の攻撃力が20%上がる</t>
+    <rPh sb="0" eb="2">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前衛位置のキャラクタの攻撃力が20%上がる、後衛位置のキャラクタの攻撃力が10%下がる</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウエイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>皇帝</t>
+    <rPh sb="0" eb="2">
+      <t>コウテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘毎にランダムで味方一人の攻撃力が50%上がる。</t>
+    <rPh sb="0" eb="2">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ゴト</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前衛位置にいるキャラクタが一人の時、そのキャラの攻撃力が50％上がる。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒトリ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教皇</t>
+    <rPh sb="0" eb="2">
+      <t>キョウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ミランダ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最も精神力の高いメンバーの最大値と同量のSPを得る。</t>
+    <rPh sb="0" eb="1">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>サイダイチ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ドウリョウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後衛位置にいるキャラクターの攻撃力が30%上がる。</t>
+    <rPh sb="0" eb="2">
+      <t>コウエイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>恋人</t>
+    <rPh sb="0" eb="2">
+      <t>コイビト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステアー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最終防衛線</t>
+    <rPh sb="0" eb="5">
+      <t>サイシュウボウエイセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>親愛度がプラスの場合、攻撃力が20％上がる</t>
+    <rPh sb="0" eb="2">
+      <t>シンアイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>親愛度が０以下の場合、攻撃力が100％上がる</t>
+    <rPh sb="0" eb="2">
+      <t>シンアイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦車</t>
+    <rPh sb="0" eb="2">
+      <t>センシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビゾン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前衛配置のキャラクターのリロード時間が20%短縮される</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンエイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力が20%上がり、リロード時間が10%遅くなる</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紅華</t>
+    <rPh sb="0" eb="1">
+      <t>クレナイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が高レベルの場合、レベル差による攻撃力､命中率減少を半分にする。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ハンブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵が低レベルの場合、レベル差による攻撃力､命中率増加を倍にする。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マギアピルグリム2章</t>
+    <rPh sb="9" eb="10">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全員の攻撃の命中率が10％上がる、距離による命中率マイナス補正を無くす。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ホセイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後衛位置にいるキャラクターの命中率が20%上がる。</t>
+    <rPh sb="0" eb="2">
+      <t>コウエイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>運命の輪</t>
+    <rPh sb="0" eb="2">
+      <t>ウンメイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(主)マギアピルグリム1章</t>
+    <rPh sb="12" eb="13">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メンバーの平均レベルで1レベル上昇できる分のストック経験点を得る。</t>
+    <rPh sb="20" eb="21">
+      <t>ブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ上の3つの敵のレベルが1上がる。</t>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒼樹</t>
+    <rPh sb="0" eb="2">
+      <t>アオキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全員の攻撃力と命中率が10％上がる</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘毎にランダムで味方一人の攻撃力と命中率が50%上がる。</t>
+    <rPh sb="0" eb="2">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ゴト</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吊るされた男</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オトコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アヤメ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘突入ごとにメンバーの誰か生命力を最大値の10%失い、他の誰か一人の攻撃力が20%上がる。</t>
+    <rPh sb="0" eb="2">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トツニュウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>サイダイチ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ウシナ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヒトリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ上の踏破済みのヘクスに、周囲のヘクスのうち一番高いレベル+1の雑魚敵と魔女が生成される。周囲のヘクスに参照できるものがない場合マップ全体からランダムにサンプルを取る。</t>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>トウハスミ</t>
+    </rPh>
+    <rPh sb="34" eb="37">
+      <t>ザコテキ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>マジョ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>シュウイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死神</t>
+    <rPh sb="0" eb="2">
+      <t>シニガミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ディーゲル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>味方全員のクリティカル率が5%、クリティカル倍率が50%上がる</t>
+    <rPh sb="0" eb="2">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メンバー全員の最大生命力が最大の30%上がる。その分生命力を得る。</t>
+    <rPh sb="7" eb="9">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>セイメイリョク</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>味方全員の攻撃の命中率が10%上がる</t>
+    <rPh sb="0" eb="2">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>味方全員のリロード時間が20％減り、命中率が10%下がる</t>
+    <rPh sb="0" eb="2">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>メイチュウリツ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪魔</t>
+    <rPh sb="0" eb="2">
+      <t>アクマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘毎にランダムで味方一人の攻撃力が50％上がり、1秒ごとに1点の生命力を失うようになる</t>
+    <rPh sb="14" eb="17">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>セイメイリョク</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ウシナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全員の精神力の上限が30％上がり、そのぶんの精神力を得る</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウゲン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>塔</t>
+    <rPh sb="0" eb="1">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天王寺さくら</t>
+    <rPh sb="0" eb="3">
+      <t>テンノウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マギアピルグリム3章</t>
+    <rPh sb="9" eb="10">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メンバーが2人以上であれば主人公以外のメンバーをランダムに喪失する。</t>
+    <rPh sb="6" eb="7">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>シュジンコウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ソウシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ上に存在する魔女のどれか一つのレベルが2上がる</t>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>マジョ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>星</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青ミク</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各キャラクタの遠近どちらかの攻撃レベルを1つ上げる</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>エンキン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>だれかの遠近攻撃レベルが1づつ上がる</t>
+    <rPh sb="4" eb="6">
+      <t>エンキン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月</t>
+    <rPh sb="0" eb="1">
+      <t>ツキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セレーネ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘後獲得するSPが1.5倍になる</t>
+    <rPh sb="0" eb="2">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メンバー全員の精神力を200増す。最大値を超えて保持される。</t>
+    <rPh sb="4" eb="6">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>サイダイチ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ホジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>太陽</t>
+    <rPh sb="0" eb="2">
+      <t>タイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サニー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘時の獲得経験値が1.3倍になる</t>
+    <rPh sb="0" eb="3">
+      <t>セントウジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ケイケンチ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ上のいくつかの敵のレベルが1上がる。</t>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>審判</t>
+    <rPh sb="0" eb="2">
+      <t>シンパン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガーネット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(主)最終防衛線</t>
+    <rPh sb="3" eb="8">
+      <t>サイシュウボウエイセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>親愛度がプラスの場合、クリティカル率が5%、クリティカル倍率が50%上がる</t>
+    <rPh sb="0" eb="2">
+      <t>シンアイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>親愛度が０以下の場合、クリティカル率が10%、クリティカル倍率が100%上がる</t>
+    <rPh sb="0" eb="2">
+      <t>シンアイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世界</t>
+    <rPh sb="0" eb="2">
+      <t>セカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>のなめ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のすべての攻撃速度、弾丸の速度、移動速度を20％遅くする</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>コウゲキソクド</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>オソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ上に存在する魔女のどれか一つのレベルが1上がる</t>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>マジョ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タロットを引くと正位置、逆位置どちらかの状態で表を向き、その効果を受ける。</t>
+    <rPh sb="5" eb="6">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>セイイチ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ギャクイチ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>オモテ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステータス画面の「影響」という場所を開くと現在持っているタロットがずらっと並び、タップすると個々の効能を確認できる。</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ココ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>コウノウ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シナリオで出現がONにされていればそのカードにまつわるキャラクターと出会い、イベントが流れた後仲間に加えるかどうか選択ができる。</t>
+    <rPh sb="5" eb="7">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>デア</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ナカマ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>008001.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>008001b.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>evx008.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>008p.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>008002.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>008002b.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>008003.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>007p.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>008004.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノア自身は攻撃はせず、浮遊するエネルギー球体(008003.png)が弾丸(008004.png)を飛ばし自律攻撃を行う。</t>
+    <rPh sb="2" eb="4">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>フユウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キュウタイ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ジリツ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネルギー球体の行動パターン</t>
+    <rPh sb="5" eb="7">
+      <t>キュウタイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・移動速度は秒速1m ・20m以内で一番近い敵に向かって移動する ・ノアから8m以上離れると移動方向をノアの方向にする 　</t>
+    <rPh sb="1" eb="5">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ビョウソク</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="46" eb="50">
+      <t>イドウホウコウ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ホウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・1秒に1回弾丸を発射する　・弾丸は命中するか射程距離10ｍ進むと爆発する。</t>
+    <rPh sb="15" eb="17">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>シャテイキョリ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>バクハツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>赤い弾丸</t>
+    <rPh sb="0" eb="1">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ダンガン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブレ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノア自身は何もしない。</t>
+    <rPh sb="2" eb="4">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵に接近されたときだけパンチを行う。</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セッキン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>命中か射程距離で半径1.5mの爆発を起こし範囲にダメージ</t>
+    <rPh sb="0" eb="2">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>シャテイキョリ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンケイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バクハツ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20+WLV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全貫通、攻撃力 60+5*WLV 接触した弾丸を消す</t>
+    <rPh sb="0" eb="1">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>カンツウ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セッショク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノアの前方1mに008004a,pngを出現させる、それは1秒かけて高さ1m、幅0.5mから高さ4m、幅6mまで拡大しながら秒速0.5ｍで前進し、同じ大きさの008004a,pngに変化したあと0.1秒ごとに秒速2mづつ加速して前進する。同じグラフィックの残像が0.1秒づつ遅れて2個重なっている。明度乗算</t>
+    <rPh sb="3" eb="5">
+      <t>ゼンポウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ハバ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ハバ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>カクダイ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ビョウソク</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ゼンシン</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>ビョウソク</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>カソク</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>ゼンシン</t>
+    </rPh>
+    <rPh sb="119" eb="120">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="128" eb="130">
+      <t>ザンゾウ</t>
+    </rPh>
+    <rPh sb="134" eb="135">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="137" eb="138">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="141" eb="142">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="142" eb="143">
+      <t>カサ</t>
+    </rPh>
+    <rPh sb="149" eb="151">
+      <t>メイド</t>
+    </rPh>
+    <rPh sb="151" eb="153">
+      <t>ジョウサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・攻撃レベルがあがると球体の数が増える　(WLV/3+2)個、最大5個。</t>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キュウタイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15秒に1回、エネルギー球の位置に直径3mのフィールドを形成する。5秒間維持される。攻撃力0 。触れた敵の属性防御力を50上げる。(弱体化する)効果は敵のデバフ抵抗力によって増減する。デバフ効果は5+WLV秒維持する。</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>チョッケイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ケイセイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ビョウカン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>イジ</t>
+    </rPh>
+    <rPh sb="42" eb="45">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="55" eb="58">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="66" eb="69">
+      <t>ジャクタイカ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="80" eb="83">
+      <t>テイコウリョク</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>ゾウゲン</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="103" eb="104">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>イジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>赤</t>
+    <rPh sb="0" eb="1">
+      <t>アカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫</t>
+    <rPh sb="0" eb="1">
+      <t>ムラサキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>緑</t>
+    <rPh sb="0" eb="1">
+      <t>ミドリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黄</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>属性防御力</t>
+    <rPh sb="0" eb="2">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>属性デバフ抵抗力</t>
+    <rPh sb="0" eb="2">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>テイコウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>リョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5350,6 +7311,34 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="MS UI Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5469,7 +7458,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5501,6 +7490,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5816,6 +7817,3510 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54209E67-297D-476E-A8A4-A10E90F6AA94}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.375" style="13" customWidth="1"/>
+    <col min="6" max="6" width="9" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>450</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>475</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43554F42-D12F-4332-9122-890BFAE92956}">
+  <dimension ref="A1:AA92"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>364</v>
+      </c>
+      <c r="I1" t="s">
+        <v>504</v>
+      </c>
+      <c r="J1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1050</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>499</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
+      </c>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>950</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>501</v>
+      </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3">
+        <v>100</v>
+      </c>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>502</v>
+      </c>
+      <c r="I4">
+        <v>125</v>
+      </c>
+      <c r="J4">
+        <v>125</v>
+      </c>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H5" t="s">
+        <v>503</v>
+      </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>365</v>
+      </c>
+      <c r="H6" t="s">
+        <v>500</v>
+      </c>
+      <c r="I6">
+        <v>75</v>
+      </c>
+      <c r="J6">
+        <v>75</v>
+      </c>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>360</v>
+      </c>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>366</v>
+      </c>
+      <c r="D13" t="s">
+        <v>340</v>
+      </c>
+      <c r="E13" t="s">
+        <v>367</v>
+      </c>
+      <c r="G13" t="s">
+        <v>357</v>
+      </c>
+      <c r="H13" t="s">
+        <v>483</v>
+      </c>
+      <c r="J13" t="s">
+        <v>361</v>
+      </c>
+      <c r="K13" t="s">
+        <v>362</v>
+      </c>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>368</v>
+      </c>
+      <c r="D14" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>371</v>
+      </c>
+      <c r="D22">
+        <v>75</v>
+      </c>
+      <c r="E22">
+        <v>0.3</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>32</v>
+      </c>
+      <c r="H22">
+        <v>15</v>
+      </c>
+      <c r="I22">
+        <v>40</v>
+      </c>
+      <c r="J22">
+        <v>10</v>
+      </c>
+      <c r="K22" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0.7</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" t="s">
+        <v>174</v>
+      </c>
+      <c r="J27" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" t="s">
+        <v>183</v>
+      </c>
+      <c r="P27" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
+        <v>372</v>
+      </c>
+      <c r="D28">
+        <v>90</v>
+      </c>
+      <c r="E28">
+        <v>0.4</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>28</v>
+      </c>
+      <c r="H28">
+        <v>4.5</v>
+      </c>
+      <c r="I28">
+        <v>1.5</v>
+      </c>
+      <c r="J28">
+        <v>10</v>
+      </c>
+      <c r="K28">
+        <v>3</v>
+      </c>
+      <c r="L28" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>373</v>
+      </c>
+      <c r="D29">
+        <v>60</v>
+      </c>
+      <c r="E29">
+        <v>0.4</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>30</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>40</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="B32" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B33" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
+        <v>371</v>
+      </c>
+      <c r="D37">
+        <v>65</v>
+      </c>
+      <c r="E37">
+        <v>0.3</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>32</v>
+      </c>
+      <c r="H37">
+        <v>15</v>
+      </c>
+      <c r="I37">
+        <v>40</v>
+      </c>
+      <c r="J37">
+        <v>10</v>
+      </c>
+      <c r="K37" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0.6</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <v>2</v>
+      </c>
+      <c r="B40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
+        <v>371</v>
+      </c>
+      <c r="D40">
+        <v>65</v>
+      </c>
+      <c r="E40">
+        <v>0.3</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>32</v>
+      </c>
+      <c r="H40">
+        <v>15</v>
+      </c>
+      <c r="I40">
+        <v>40</v>
+      </c>
+      <c r="J40">
+        <v>10</v>
+      </c>
+      <c r="K40" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <v>2</v>
+      </c>
+      <c r="B41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0.6</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A43">
+        <v>3</v>
+      </c>
+      <c r="B43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" t="s">
+        <v>371</v>
+      </c>
+      <c r="D43">
+        <v>65</v>
+      </c>
+      <c r="E43">
+        <v>0.3</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>32</v>
+      </c>
+      <c r="H43">
+        <v>15</v>
+      </c>
+      <c r="I43">
+        <v>40</v>
+      </c>
+      <c r="J43">
+        <v>10</v>
+      </c>
+      <c r="K43" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0.6</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A46">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" t="s">
+        <v>371</v>
+      </c>
+      <c r="D46">
+        <v>65</v>
+      </c>
+      <c r="E46">
+        <v>0.3</v>
+      </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
+      <c r="G46">
+        <v>32</v>
+      </c>
+      <c r="H46">
+        <v>15</v>
+      </c>
+      <c r="I46">
+        <v>40</v>
+      </c>
+      <c r="J46">
+        <v>10</v>
+      </c>
+      <c r="K46" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0.6</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A49">
+        <v>5</v>
+      </c>
+      <c r="B49" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" t="s">
+        <v>371</v>
+      </c>
+      <c r="D49">
+        <v>65</v>
+      </c>
+      <c r="E49">
+        <v>0.3</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="G49">
+        <v>32</v>
+      </c>
+      <c r="H49">
+        <v>15</v>
+      </c>
+      <c r="I49">
+        <v>40</v>
+      </c>
+      <c r="J49">
+        <v>10</v>
+      </c>
+      <c r="K49" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A50">
+        <v>5</v>
+      </c>
+      <c r="B50" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0.6</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A52">
+        <v>6</v>
+      </c>
+      <c r="B52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" t="s">
+        <v>371</v>
+      </c>
+      <c r="D52">
+        <v>65</v>
+      </c>
+      <c r="E52">
+        <v>0.3</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52">
+        <v>32</v>
+      </c>
+      <c r="H52">
+        <v>15</v>
+      </c>
+      <c r="I52">
+        <v>40</v>
+      </c>
+      <c r="J52">
+        <v>10</v>
+      </c>
+      <c r="K52" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A53">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0.6</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A55">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" t="s">
+        <v>371</v>
+      </c>
+      <c r="D55">
+        <v>65</v>
+      </c>
+      <c r="E55">
+        <v>0.3</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
+      <c r="G55">
+        <v>32</v>
+      </c>
+      <c r="H55">
+        <v>15</v>
+      </c>
+      <c r="I55">
+        <v>40</v>
+      </c>
+      <c r="J55">
+        <v>10</v>
+      </c>
+      <c r="K55" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A56">
+        <v>7</v>
+      </c>
+      <c r="B56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0.6</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" t="s">
+        <v>174</v>
+      </c>
+      <c r="J58" t="s">
+        <v>21</v>
+      </c>
+      <c r="K58" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A59">
+        <v>1</v>
+      </c>
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" t="s">
+        <v>372</v>
+      </c>
+      <c r="D59">
+        <v>70</v>
+      </c>
+      <c r="E59">
+        <v>0.4</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>28</v>
+      </c>
+      <c r="H59">
+        <v>4.5</v>
+      </c>
+      <c r="I59">
+        <v>1.5</v>
+      </c>
+      <c r="J59">
+        <v>10</v>
+      </c>
+      <c r="K59">
+        <v>3</v>
+      </c>
+      <c r="L59" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A60">
+        <v>1</v>
+      </c>
+      <c r="B60" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" t="s">
+        <v>373</v>
+      </c>
+      <c r="D60">
+        <v>40</v>
+      </c>
+      <c r="E60">
+        <v>0.4</v>
+      </c>
+      <c r="F60">
+        <v>2</v>
+      </c>
+      <c r="G60">
+        <v>30</v>
+      </c>
+      <c r="H60">
+        <v>2</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="J60">
+        <v>40</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A62">
+        <v>2</v>
+      </c>
+      <c r="B62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" t="s">
+        <v>372</v>
+      </c>
+      <c r="D62">
+        <v>70</v>
+      </c>
+      <c r="E62">
+        <v>0.4</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>28</v>
+      </c>
+      <c r="H62">
+        <v>4.5</v>
+      </c>
+      <c r="I62">
+        <v>1.5</v>
+      </c>
+      <c r="J62">
+        <v>10</v>
+      </c>
+      <c r="K62">
+        <v>3</v>
+      </c>
+      <c r="L62" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A63">
+        <v>2</v>
+      </c>
+      <c r="B63" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63" t="s">
+        <v>373</v>
+      </c>
+      <c r="D63">
+        <v>40</v>
+      </c>
+      <c r="E63">
+        <v>0.4</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+      <c r="G63">
+        <v>30</v>
+      </c>
+      <c r="H63">
+        <v>2</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63">
+        <v>40</v>
+      </c>
+      <c r="K63">
+        <v>1</v>
+      </c>
+      <c r="L63" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A65">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65" t="s">
+        <v>372</v>
+      </c>
+      <c r="D65">
+        <v>70</v>
+      </c>
+      <c r="E65">
+        <v>0.4</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>28</v>
+      </c>
+      <c r="H65">
+        <v>4.5</v>
+      </c>
+      <c r="I65">
+        <v>1.5</v>
+      </c>
+      <c r="J65">
+        <v>10</v>
+      </c>
+      <c r="K65">
+        <v>3</v>
+      </c>
+      <c r="L65" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A66">
+        <v>3</v>
+      </c>
+      <c r="B66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" t="s">
+        <v>373</v>
+      </c>
+      <c r="D66">
+        <v>40</v>
+      </c>
+      <c r="E66">
+        <v>0.4</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+      <c r="G66">
+        <v>30</v>
+      </c>
+      <c r="H66">
+        <v>2</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="J66">
+        <v>40</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A68">
+        <v>4</v>
+      </c>
+      <c r="B68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" t="s">
+        <v>372</v>
+      </c>
+      <c r="D68">
+        <v>70</v>
+      </c>
+      <c r="E68">
+        <v>0.4</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>28</v>
+      </c>
+      <c r="H68">
+        <v>4.5</v>
+      </c>
+      <c r="I68">
+        <v>1.5</v>
+      </c>
+      <c r="J68">
+        <v>10</v>
+      </c>
+      <c r="K68">
+        <v>3</v>
+      </c>
+      <c r="L68" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A69">
+        <v>4</v>
+      </c>
+      <c r="B69" t="s">
+        <v>25</v>
+      </c>
+      <c r="C69" t="s">
+        <v>373</v>
+      </c>
+      <c r="D69">
+        <v>40</v>
+      </c>
+      <c r="E69">
+        <v>0.4</v>
+      </c>
+      <c r="F69">
+        <v>3</v>
+      </c>
+      <c r="G69">
+        <v>30</v>
+      </c>
+      <c r="H69">
+        <v>2</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+      <c r="J69">
+        <v>40</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+      <c r="L69" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A71">
+        <v>5</v>
+      </c>
+      <c r="B71" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71" t="s">
+        <v>372</v>
+      </c>
+      <c r="D71">
+        <v>70</v>
+      </c>
+      <c r="E71">
+        <v>0.4</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>28</v>
+      </c>
+      <c r="H71">
+        <v>4.5</v>
+      </c>
+      <c r="I71">
+        <v>1.5</v>
+      </c>
+      <c r="J71">
+        <v>10</v>
+      </c>
+      <c r="K71">
+        <v>3</v>
+      </c>
+      <c r="L71" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A72">
+        <v>5</v>
+      </c>
+      <c r="B72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C72" t="s">
+        <v>373</v>
+      </c>
+      <c r="D72">
+        <v>40</v>
+      </c>
+      <c r="E72">
+        <v>0.4</v>
+      </c>
+      <c r="F72">
+        <v>3</v>
+      </c>
+      <c r="G72">
+        <v>30</v>
+      </c>
+      <c r="H72">
+        <v>2</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>40</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
+      </c>
+      <c r="L72" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A74">
+        <v>6</v>
+      </c>
+      <c r="B74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C74" t="s">
+        <v>372</v>
+      </c>
+      <c r="D74">
+        <v>70</v>
+      </c>
+      <c r="E74">
+        <v>0.4</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>28</v>
+      </c>
+      <c r="H74">
+        <v>4.5</v>
+      </c>
+      <c r="I74">
+        <v>1.5</v>
+      </c>
+      <c r="J74">
+        <v>10</v>
+      </c>
+      <c r="K74">
+        <v>3</v>
+      </c>
+      <c r="L74" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A75">
+        <v>6</v>
+      </c>
+      <c r="B75" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" t="s">
+        <v>373</v>
+      </c>
+      <c r="D75">
+        <v>40</v>
+      </c>
+      <c r="E75">
+        <v>0.4</v>
+      </c>
+      <c r="F75">
+        <v>3</v>
+      </c>
+      <c r="G75">
+        <v>30</v>
+      </c>
+      <c r="H75">
+        <v>2</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75">
+        <v>40</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="L75" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A77">
+        <v>7</v>
+      </c>
+      <c r="B77" t="s">
+        <v>25</v>
+      </c>
+      <c r="C77" t="s">
+        <v>372</v>
+      </c>
+      <c r="D77">
+        <v>70</v>
+      </c>
+      <c r="E77">
+        <v>0.4</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77">
+        <v>28</v>
+      </c>
+      <c r="H77">
+        <v>4.5</v>
+      </c>
+      <c r="I77">
+        <v>1.5</v>
+      </c>
+      <c r="J77">
+        <v>10</v>
+      </c>
+      <c r="K77">
+        <v>3</v>
+      </c>
+      <c r="L77" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A78">
+        <v>7</v>
+      </c>
+      <c r="B78" t="s">
+        <v>25</v>
+      </c>
+      <c r="C78" t="s">
+        <v>373</v>
+      </c>
+      <c r="D78">
+        <v>40</v>
+      </c>
+      <c r="E78">
+        <v>0.4</v>
+      </c>
+      <c r="F78">
+        <v>4</v>
+      </c>
+      <c r="G78">
+        <v>30</v>
+      </c>
+      <c r="H78">
+        <v>2</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78">
+        <v>40</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="L78" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A88" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>39</v>
+      </c>
+      <c r="B90" t="s">
+        <v>100</v>
+      </c>
+      <c r="D90" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A92" s="11" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEE9B92-785A-48AE-9C69-B456B774F658}">
+  <dimension ref="A1:AA96"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>404</v>
+      </c>
+      <c r="I1" t="s">
+        <v>504</v>
+      </c>
+      <c r="J1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>800</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>499</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
+      </c>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1200</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>501</v>
+      </c>
+      <c r="I3">
+        <v>75</v>
+      </c>
+      <c r="J3">
+        <v>75</v>
+      </c>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>502</v>
+      </c>
+      <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" t="s">
+        <v>503</v>
+      </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>485</v>
+      </c>
+      <c r="H6" t="s">
+        <v>500</v>
+      </c>
+      <c r="I6">
+        <v>125</v>
+      </c>
+      <c r="J6">
+        <v>125</v>
+      </c>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>486</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>2</v>
+      </c>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>487</v>
+      </c>
+      <c r="P8">
+        <v>2</v>
+      </c>
+      <c r="Q8">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>488</v>
+      </c>
+      <c r="P9">
+        <v>3</v>
+      </c>
+      <c r="Q9">
+        <v>2</v>
+      </c>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>497</v>
+      </c>
+      <c r="P10">
+        <v>4</v>
+      </c>
+      <c r="Q10">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="P11">
+        <v>5</v>
+      </c>
+      <c r="Q11">
+        <v>3</v>
+      </c>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="P12">
+        <v>6</v>
+      </c>
+      <c r="Q12">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>403</v>
+      </c>
+      <c r="P13">
+        <v>7</v>
+      </c>
+      <c r="Q13">
+        <v>3</v>
+      </c>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>476</v>
+      </c>
+      <c r="D14" t="s">
+        <v>340</v>
+      </c>
+      <c r="E14" t="s">
+        <v>477</v>
+      </c>
+      <c r="G14" t="s">
+        <v>357</v>
+      </c>
+      <c r="H14" t="s">
+        <v>479</v>
+      </c>
+      <c r="J14" t="s">
+        <v>361</v>
+      </c>
+      <c r="K14" t="s">
+        <v>478</v>
+      </c>
+      <c r="P14">
+        <v>8</v>
+      </c>
+      <c r="Q14">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>480</v>
+      </c>
+      <c r="D15" t="s">
+        <v>481</v>
+      </c>
+      <c r="P15">
+        <v>9</v>
+      </c>
+      <c r="Q15">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="9"/>
+      <c r="AA15" s="9"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>482</v>
+      </c>
+      <c r="D16" t="s">
+        <v>484</v>
+      </c>
+      <c r="P16">
+        <v>10</v>
+      </c>
+      <c r="Q16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="P17">
+        <v>11</v>
+      </c>
+      <c r="Q17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>135</v>
+      </c>
+      <c r="P18">
+        <v>12</v>
+      </c>
+      <c r="Q18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>489</v>
+      </c>
+      <c r="D23">
+        <v>50</v>
+      </c>
+      <c r="E23">
+        <v>0.5</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>20</v>
+      </c>
+      <c r="H23">
+        <v>10</v>
+      </c>
+      <c r="I23">
+        <v>20</v>
+      </c>
+      <c r="J23">
+        <v>5</v>
+      </c>
+      <c r="K23" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0.5</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B26" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s">
+        <v>174</v>
+      </c>
+      <c r="J28" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" t="s">
+        <v>183</v>
+      </c>
+      <c r="T28" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>373</v>
+      </c>
+      <c r="D30">
+        <v>60</v>
+      </c>
+      <c r="E30">
+        <v>0.4</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>30</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>40</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="B32" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B33" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
+        <v>489</v>
+      </c>
+      <c r="D38">
+        <v>50</v>
+      </c>
+      <c r="E38">
+        <v>0.5</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>20</v>
+      </c>
+      <c r="H38">
+        <v>10</v>
+      </c>
+      <c r="I38">
+        <v>20</v>
+      </c>
+      <c r="J38">
+        <v>5</v>
+      </c>
+      <c r="K38" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <v>1</v>
+      </c>
+      <c r="B39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0.5</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <v>2</v>
+      </c>
+      <c r="B41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
+        <v>489</v>
+      </c>
+      <c r="D41">
+        <v>50</v>
+      </c>
+      <c r="E41">
+        <v>0.5</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>20</v>
+      </c>
+      <c r="H41">
+        <v>10</v>
+      </c>
+      <c r="I41">
+        <v>20</v>
+      </c>
+      <c r="J41">
+        <v>5</v>
+      </c>
+      <c r="K41" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <v>2</v>
+      </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0.5</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" t="s">
+        <v>489</v>
+      </c>
+      <c r="D44">
+        <v>50</v>
+      </c>
+      <c r="E44">
+        <v>0.5</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>20</v>
+      </c>
+      <c r="H44">
+        <v>10</v>
+      </c>
+      <c r="I44">
+        <v>20</v>
+      </c>
+      <c r="J44">
+        <v>5</v>
+      </c>
+      <c r="K44" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0.5</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" t="s">
+        <v>489</v>
+      </c>
+      <c r="D47">
+        <v>50</v>
+      </c>
+      <c r="E47">
+        <v>0.5</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>20</v>
+      </c>
+      <c r="H47">
+        <v>10</v>
+      </c>
+      <c r="I47">
+        <v>20</v>
+      </c>
+      <c r="J47">
+        <v>5</v>
+      </c>
+      <c r="K47" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0.5</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A50">
+        <v>5</v>
+      </c>
+      <c r="B50" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" t="s">
+        <v>489</v>
+      </c>
+      <c r="D50">
+        <v>50</v>
+      </c>
+      <c r="E50">
+        <v>0.5</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>20</v>
+      </c>
+      <c r="H50">
+        <v>10</v>
+      </c>
+      <c r="I50">
+        <v>20</v>
+      </c>
+      <c r="J50">
+        <v>5</v>
+      </c>
+      <c r="K50" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A51">
+        <v>5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0.5</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A53">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" t="s">
+        <v>489</v>
+      </c>
+      <c r="D53">
+        <v>50</v>
+      </c>
+      <c r="E53">
+        <v>0.5</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>20</v>
+      </c>
+      <c r="H53">
+        <v>10</v>
+      </c>
+      <c r="I53">
+        <v>20</v>
+      </c>
+      <c r="J53">
+        <v>5</v>
+      </c>
+      <c r="K53" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A54">
+        <v>6</v>
+      </c>
+      <c r="B54" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0.5</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A56">
+        <v>7</v>
+      </c>
+      <c r="B56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" t="s">
+        <v>489</v>
+      </c>
+      <c r="D56">
+        <v>50</v>
+      </c>
+      <c r="E56">
+        <v>0.5</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>20</v>
+      </c>
+      <c r="H56">
+        <v>10</v>
+      </c>
+      <c r="I56">
+        <v>20</v>
+      </c>
+      <c r="J56">
+        <v>5</v>
+      </c>
+      <c r="K56" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A57">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0.5</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s">
+        <v>174</v>
+      </c>
+      <c r="J59" t="s">
+        <v>21</v>
+      </c>
+      <c r="K59" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A61">
+        <v>1</v>
+      </c>
+      <c r="B61" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" t="s">
+        <v>373</v>
+      </c>
+      <c r="D61">
+        <v>60</v>
+      </c>
+      <c r="E61">
+        <v>0.4</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>30</v>
+      </c>
+      <c r="H61">
+        <v>2</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>40</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+      <c r="L61" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A64">
+        <v>2</v>
+      </c>
+      <c r="B64" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" t="s">
+        <v>373</v>
+      </c>
+      <c r="D64">
+        <v>60</v>
+      </c>
+      <c r="E64">
+        <v>0.4</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>30</v>
+      </c>
+      <c r="H64">
+        <v>2</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>40</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A67">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" t="s">
+        <v>373</v>
+      </c>
+      <c r="D67">
+        <v>60</v>
+      </c>
+      <c r="E67">
+        <v>0.4</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>30</v>
+      </c>
+      <c r="H67">
+        <v>2</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67">
+        <v>40</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A69">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A70">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70" t="s">
+        <v>373</v>
+      </c>
+      <c r="D70">
+        <v>60</v>
+      </c>
+      <c r="E70">
+        <v>0.4</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>30</v>
+      </c>
+      <c r="H70">
+        <v>2</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70">
+        <v>40</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A72">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A73">
+        <v>5</v>
+      </c>
+      <c r="B73" t="s">
+        <v>25</v>
+      </c>
+      <c r="C73" t="s">
+        <v>373</v>
+      </c>
+      <c r="D73">
+        <v>60</v>
+      </c>
+      <c r="E73">
+        <v>0.4</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
+        <v>30</v>
+      </c>
+      <c r="H73">
+        <v>2</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+      <c r="J73">
+        <v>40</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
+      </c>
+      <c r="L73" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A75">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A76">
+        <v>6</v>
+      </c>
+      <c r="B76" t="s">
+        <v>25</v>
+      </c>
+      <c r="C76" t="s">
+        <v>373</v>
+      </c>
+      <c r="D76">
+        <v>60</v>
+      </c>
+      <c r="E76">
+        <v>0.4</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>30</v>
+      </c>
+      <c r="H76">
+        <v>2</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <v>40</v>
+      </c>
+      <c r="K76">
+        <v>1</v>
+      </c>
+      <c r="L76" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A78">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A79">
+        <v>7</v>
+      </c>
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" t="s">
+        <v>373</v>
+      </c>
+      <c r="D79">
+        <v>60</v>
+      </c>
+      <c r="E79">
+        <v>0.4</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>30</v>
+      </c>
+      <c r="H79">
+        <v>2</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79">
+        <v>40</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>39</v>
+      </c>
+      <c r="B91" t="s">
+        <v>494</v>
+      </c>
+      <c r="D91" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A92" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A96" s="10"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF8D88E9-94CD-49D3-A71A-3DD1767249D5}">
   <dimension ref="A1:C127"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -6495,7 +12000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9CB837D-4EBE-4F79-AFA5-7C29098E884F}">
   <dimension ref="A1:B77"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -6852,7 +12357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3BDEEA5-0C52-418A-869D-763A08A86B98}">
   <dimension ref="A1:X90"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -8386,7 +13891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{741D4FE6-ED91-42FF-8EA8-625E7642B1DC}">
   <dimension ref="A1:AA70"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -9725,7 +15230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABCC4FB2-6D08-4B07-803F-CE542E141D53}">
   <dimension ref="A1:AC100"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -11869,14 +17374,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D03FCA2-BC20-4F8C-9DB1-6D5B1B890C80}">
   <dimension ref="A1:AC93"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>363</v>
       </c>
       <c r="P1" t="s">
         <v>69</v>
@@ -13789,7 +19294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D99D84-1F2C-4291-8794-B76CD74047D9}">
   <dimension ref="A1:AC94"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -15712,7 +21217,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1462EC-F2B4-4748-B5F2-4C03CEBAE5D3}">
   <dimension ref="A1:AA91"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>

--- a/public/files/DATA/CHR_data.xlsx
+++ b/public/files/DATA/CHR_data.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63841D2-380C-4CDD-AD97-8888C84354F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583ECDD9-C5FD-41AA-BF8C-37C9821AEBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="855" yWindow="225" windowWidth="26205" windowHeight="14850" activeTab="10" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
+    <workbookView xWindow="420" yWindow="180" windowWidth="26205" windowHeight="14850" firstSheet="2" activeTab="13" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
   </bookViews>
   <sheets>
-    <sheet name="tarot" sheetId="15" r:id="rId1"/>
-    <sheet name="共通ﾃﾞｰﾀ" sheetId="9" r:id="rId2"/>
-    <sheet name="メイン進行ルーチン" sheetId="10" r:id="rId3"/>
+    <sheet name="共通ﾃﾞｰﾀ" sheetId="9" r:id="rId1"/>
+    <sheet name="メイン進行ルーチン" sheetId="10" r:id="rId2"/>
+    <sheet name="tarot" sheetId="15" r:id="rId3"/>
     <sheet name="10紫苑" sheetId="4" r:id="rId4"/>
     <sheet name="15李乃果data" sheetId="2" r:id="rId5"/>
     <sheet name="12蒼樹" sheetId="6" r:id="rId6"/>
@@ -24,6 +24,9 @@
     <sheet name="9白蓮" sheetId="11" r:id="rId9"/>
     <sheet name="0ななよ" sheetId="13" r:id="rId10"/>
     <sheet name="4ノア" sheetId="14" r:id="rId11"/>
+    <sheet name="009リフィエル" sheetId="18" r:id="rId12"/>
+    <sheet name="010プロセル" sheetId="16" r:id="rId13"/>
+    <sheet name="MKP" sheetId="19" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2305" uniqueCount="603">
   <si>
     <t>李乃果</t>
     <rPh sb="0" eb="1">
@@ -5326,9 +5329,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>進む距離は15m？にしてたと思うけど8mとして。その爆発は5秒+（WLV/2）秒持続し、敵にダメージを与え続け(攻撃力の10%+WLV％)、弾丸を吸収し続ける。　</t>
-  </si>
-  <si>
     <t>愚者</t>
     <rPh sb="0" eb="2">
       <t>グシャ</t>
@@ -5923,10 +5923,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ミランダ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>最も精神力の高いメンバーの最大値と同量のSPを得る。</t>
     <rPh sb="0" eb="1">
       <t>モット</t>
@@ -7283,6 +7279,1518 @@
     </rPh>
     <rPh sb="7" eb="8">
       <t>リョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ノア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>進む距離は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>15m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>？にしてたと思うけど</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>として。その爆発は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>秒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>WLV/2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>）秒持続し、敵にダメージを与え続け</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>攻撃力の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>10%+WLV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>％</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>、弾丸を吸収し続ける。　</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紫</t>
+    <rPh sb="0" eb="1">
+      <t>ムラサキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>氷の塊を飛ばし、命中または射程いっぱいで爆発して周辺に凍結フィールドを形成する。</t>
+    <rPh sb="0" eb="1">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カタマリ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シャテイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>バクハツ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シュウヘン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>トウケツ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ケイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近接では速い速度でつららを発生させて飛ばす。</t>
+    <rPh sb="0" eb="2">
+      <t>キンセツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SPによる回復を行うことができず、精神力を失うと消える。</t>
+    <rPh sb="5" eb="7">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ウシナ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リフィエル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技を発動すると一定時間大人の姿になり紅華のように槍で戦う。</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>オトナ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>スガタ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ヤリ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>タタカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通常時は仲間に回復、バリアの展開、敵へのデバフを行う。</t>
+    <rPh sb="0" eb="3">
+      <t>ツウジョウジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ナカマ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>テンカイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>009001.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>009001b.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>009p.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>evx009.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>009002.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>009002b.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>009003.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技を発動すると10+WLV秒の間姿が変わる。</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>スガタ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>槍回しの射程内に敵が居ない場合、槍投げを行う。</t>
+    <rPh sb="0" eb="1">
+      <t>ヤリ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シャテイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヤリ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>花粉煙幕</t>
+    <rPh sb="0" eb="2">
+      <t>カフン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>エンマク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>命中か射程距離で半径1.5mの爆発を起こし2秒持続、範囲に防御力減少5秒(全属性値50UP)、弾丸を吸収する。</t>
+    <rPh sb="0" eb="2">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>シャテイキョリ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンケイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バクハツ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジゾク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="37" eb="41">
+      <t>ゼンゾクセイチ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>キュウシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージを与える攻撃は行わない。</t>
+    <rPh sb="5" eb="6">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リフィエルは敵が近くても遠くても行動パターンは同じ。</t>
+    <rPh sb="6" eb="7">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>オナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つらら大</t>
+    <rPh sb="3" eb="4">
+      <t>ダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">減衰1/3貫通　命中か射程距離で半径1.5mの氷塊(008004.png)を作り2秒維持、範囲にダメージ(攻撃力の10%) </t>
+    <rPh sb="0" eb="2">
+      <t>ゲンスイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンツウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>メイチュウ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>シャテイキョリ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハンケイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒョウカイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>イジ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="53" eb="56">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つらら小</t>
+    <rPh sb="3" eb="4">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つらら大、つらら小の発射時、本体中心ではなく本体中心から距離1mのランダム位置から発射される。</t>
+    <rPh sb="3" eb="4">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハッシャ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>ホンタイチュウシン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ハッシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>減衰1/3貫通</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンスイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンツウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10秒に1回、自身の2m前に氷塊(008004.png)を生成する。直径1.5mまで拡大し、敵の弾丸を5+WLVぶん吸収するか、6秒経過で消える</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カタマリ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>チョッケイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>カクダイ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>キュウシュウ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ケイカ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10秒に1回、自身の8m前に氷塊(008004.png)を生成する。直径1.5mまで拡大し、敵の弾丸を5+WLVぶん吸収するか、6秒経過で消える</t>
+    <rPh sb="2" eb="3">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>コオリ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カタマリ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>チョッケイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>カクダイ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ダンガン</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>キュウシュウ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ケイカ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※つらら大、つらら小の発射時、本体中心ではなく本体中心から距離1mのランダム位置から発射される。</t>
+    <rPh sb="4" eb="5">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハッシャ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ホンタイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>ホンタイチュウシン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ハッシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標を設定せず、つらら大とつらら小を真上から左右に5度づつランダムな角度に乱射する。</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>マウエ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>サユウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ランシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>射程距離分進むとつらら小は消え、つらら大は氷塊を生成する。</t>
+    <rPh sb="0" eb="5">
+      <t>シャテイキョリブン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒョウカイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つらら大を0.4秒に1発、つらら小を0.2秒に1発、3秒間+(WLV/3)秒間乱射する。</t>
+    <rPh sb="3" eb="4">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ハツ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ハツ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ビョウカン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ビョウカン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ランシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リロード時間 30秒-WLV*2</t>
+    <rPh sb="4" eb="6">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>010001.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>010002.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>010003.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>010001b.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>010002b.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>010004.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>010p.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>evx010.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔法少女強化プログラム</t>
+    <rPh sb="0" eb="4">
+      <t>マホウショウジョ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセルが作った魔法少女の強化システム。</t>
+    <rPh sb="5" eb="6">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>マホウショウジョ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SPを消費して強化を購入することができる。</t>
+    <rPh sb="3" eb="5">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎HP+100</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎強化II</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎強化I</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎強化III</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SPを支払うことで能力を獲得できる。</t>
+    <rPh sb="3" eb="5">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎強化IV</t>
+    <rPh sb="0" eb="4">
+      <t>キソキョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎強化V</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎攻撃力を10上げる。</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎回避率を5%上げる。</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>カイヒリツ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎HP成長率を2%上げる</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>セイチョウリツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機敏性強化</t>
+    <rPh sb="0" eb="3">
+      <t>キビンセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻性潜在力強化</t>
+    <rPh sb="0" eb="1">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>センザイリョク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻性強化</t>
+    <rPh sb="0" eb="1">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機敏性潜在力強化</t>
+    <rPh sb="0" eb="2">
+      <t>キビン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>センザイリョク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎攻撃力成長率を2%上げる</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>セイチョウリツ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SPを使ったMPの回復効率を10%上げる(効率0.1％→0.11%に)</t>
+    <rPh sb="3" eb="4">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>カイフクコウリツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>コウリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎MP+100</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WAZA学科</t>
+    <rPh sb="4" eb="6">
+      <t>ガッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎MP成長率を2%上げる</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>セイチョウリツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎CH率強化</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎CH倍率強化</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CH率が3％上がる</t>
+    <rPh sb="2" eb="3">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CH倍率が30％上がる</t>
+    <rPh sb="2" eb="4">
+      <t>バイリツ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KOKORO学科</t>
+    <rPh sb="6" eb="8">
+      <t>ガッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KARADA学科</t>
+    <rPh sb="6" eb="8">
+      <t>ガッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Aカテゴリをすべて履修するとB,C,Dのどれかを選択できるようになる。</t>
+    <rPh sb="9" eb="11">
+      <t>リシュウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KISO学科</t>
+    <rPh sb="4" eb="6">
+      <t>ガッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>精神洗浄効率強化</t>
+    <rPh sb="0" eb="2">
+      <t>セイシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>センジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウリツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>呼吸法訓練</t>
+    <rPh sb="0" eb="3">
+      <t>コキュウホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>クンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>精神潜在力強化</t>
+    <rPh sb="0" eb="2">
+      <t>セイシン</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>センザイリョク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎精神力強化</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>セイシンリョク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>治癒力強化</t>
+    <rPh sb="0" eb="3">
+      <t>チユリョク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生命潜在力強化</t>
+    <rPh sb="0" eb="2">
+      <t>セイメイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>センザイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎生命力強化</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>栄養回収率強化</t>
+    <rPh sb="0" eb="2">
+      <t>エイヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイシュウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎抵抗力強化</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>テイコウリョク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各属性防御力、デバフ抵抗率が3下がる(ダメージ、効果が3%減少する)</t>
+    <rPh sb="0" eb="3">
+      <t>カクゾクセイ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>テイコウリツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B,C,Dは5種類完了するともう一度5種を履修できるようになる。全部で5段階まで行える。</t>
+    <rPh sb="7" eb="9">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>シュ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>リシュウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ゼンブ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ダンカイ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘中のSP減少を緩和する(10%減少)</t>
+    <rPh sb="0" eb="3">
+      <t>セントウチュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンワ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MP回復時のSP減少を緩和する　MP1→HP33</t>
+    <rPh sb="2" eb="4">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラクターレベル1ごとに回避率が0.5%上がるようになる</t>
+    <rPh sb="13" eb="16">
+      <t>カイヒリツ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘中のSP減少を緩和する(10%減少)</t>
+    <rPh sb="0" eb="3">
+      <t>セントウチュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP回復時のMP減少を10%緩和する</t>
+    <rPh sb="2" eb="4">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>食料消耗を10%減らす(1人編成時の値、メンバー割で減少率が減っていく。)</t>
+    <rPh sb="0" eb="2">
+      <t>ショクリョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウモウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ヘンセイジ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ワリ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>ゲンショウリツ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヘ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>費用は(訓練回数+1)*50</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヨウ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>クンレンカイスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初心者はまずA学科の全履修を求められる。</t>
+    <rPh sb="0" eb="3">
+      <t>ショシンシャ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガッカ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ゼンリシュウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>モト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1回訓練するとその学科のうちどれかの科目をランダムで履修する。同じものを履修することはない。</t>
+    <rPh sb="1" eb="2">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>クンレン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガッカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カモク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>リシュウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>リシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔法少女毎に訓練回数が記録される。</t>
+    <rPh sb="0" eb="4">
+      <t>マホウショウジョ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ゴト</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>クンレン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7291,7 +8799,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7339,6 +8847,18 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -7458,7 +8978,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7502,6 +9022,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7817,488 +9340,677 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54209E67-297D-476E-A8A4-A10E90F6AA94}">
-  <dimension ref="A1:F27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF8D88E9-94CD-49D3-A71A-3DD1767249D5}">
+  <dimension ref="A1:C127"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="61.375" style="13" customWidth="1"/>
-    <col min="6" max="6" width="9" style="13"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>382</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>393</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>64000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>128000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>256000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>223</v>
+      </c>
+      <c r="B15">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>236</v>
+      </c>
+      <c r="B35" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <v>1</v>
+      </c>
+      <c r="B37">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38">
         <v>2</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5">
+      <c r="B38">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39">
         <v>3</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="D5" s="12" t="s">
+      <c r="B39">
         <v>400</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>401</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40">
         <v>4</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7">
+      <c r="B40">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A41">
         <v>5</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>409</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8">
+      <c r="B41">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A42">
         <v>6</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>414</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9">
+      <c r="B42">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A43">
         <v>7</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>416</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>418</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10">
+      <c r="B43">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A44">
         <v>8</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>421</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11">
+      <c r="B44">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A45">
         <v>9</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>424</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12">
+      <c r="B45">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A46">
         <v>10</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>426</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>427</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13">
+      <c r="B46">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A47">
         <v>11</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14">
+      <c r="B47">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A48">
         <v>12</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>434</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15">
+      <c r="B48">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>84</v>
+      </c>
+      <c r="B54" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>74</v>
+      </c>
+      <c r="C57" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>75</v>
+      </c>
+      <c r="C58" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A74" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A75" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A76" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A78" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A88" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A92" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A116" t="s">
+        <v>325</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
+        <v>323</v>
+      </c>
+      <c r="B117">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A118" t="s">
+        <v>324</v>
+      </c>
+      <c r="B118">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
+        <v>326</v>
+      </c>
+      <c r="B119">
         <v>13</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>443</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>444</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>448</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19">
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A120" t="s">
+        <v>327</v>
+      </c>
+      <c r="B120">
         <v>17</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>452</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>453</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>454</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>456</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>457</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>458</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>461</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>462</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>464</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>466</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>469</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>470</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>475</v>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A126" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A127" t="s">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -8314,13 +10026,13 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="J1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.4">
@@ -8334,7 +10046,7 @@
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="I2">
         <v>100</v>
@@ -8356,7 +10068,7 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="I3">
         <v>100</v>
@@ -8378,7 +10090,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I4">
         <v>125</v>
@@ -8403,7 +10115,7 @@
         <v>181</v>
       </c>
       <c r="H5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -8416,10 +10128,10 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="I6">
         <v>75</v>
@@ -8464,7 +10176,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z12" s="9"/>
       <c r="AA12" s="9"/>
@@ -8474,25 +10186,25 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D13" t="s">
         <v>340</v>
       </c>
       <c r="E13" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G13" t="s">
         <v>357</v>
       </c>
       <c r="H13" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J13" t="s">
+        <v>360</v>
+      </c>
+      <c r="K13" t="s">
         <v>361</v>
-      </c>
-      <c r="K13" t="s">
-        <v>362</v>
       </c>
       <c r="Z13" s="9"/>
       <c r="AA13" s="9"/>
@@ -8502,10 +10214,10 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
+        <v>367</v>
+      </c>
+      <c r="D14" t="s">
         <v>368</v>
-      </c>
-      <c r="D14" t="s">
-        <v>369</v>
       </c>
       <c r="Z14" s="9"/>
       <c r="AA14" s="9"/>
@@ -8515,7 +10227,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.4">
@@ -8567,7 +10279,7 @@
         <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D22">
         <v>75</v>
@@ -8591,7 +10303,7 @@
         <v>10</v>
       </c>
       <c r="K22" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.4">
@@ -8672,7 +10384,7 @@
         <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D28">
         <v>90</v>
@@ -8699,7 +10411,7 @@
         <v>3</v>
       </c>
       <c r="L28" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.4">
@@ -8710,7 +10422,7 @@
         <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D29">
         <v>60</v>
@@ -8742,12 +10454,12 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B32" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.4">
@@ -8787,7 +10499,7 @@
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D37">
         <v>65</v>
@@ -8811,7 +10523,7 @@
         <v>10</v>
       </c>
       <c r="K37" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.4">
@@ -8857,7 +10569,7 @@
         <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D40">
         <v>65</v>
@@ -8881,7 +10593,7 @@
         <v>10</v>
       </c>
       <c r="K40" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.4">
@@ -8927,7 +10639,7 @@
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D43">
         <v>65</v>
@@ -8951,7 +10663,7 @@
         <v>10</v>
       </c>
       <c r="K43" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.4">
@@ -8997,7 +10709,7 @@
         <v>22</v>
       </c>
       <c r="C46" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D46">
         <v>65</v>
@@ -9021,7 +10733,7 @@
         <v>10</v>
       </c>
       <c r="K46" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.4">
@@ -9067,7 +10779,7 @@
         <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D49">
         <v>65</v>
@@ -9091,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="K49" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.4">
@@ -9137,7 +10849,7 @@
         <v>22</v>
       </c>
       <c r="C52" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D52">
         <v>65</v>
@@ -9161,7 +10873,7 @@
         <v>10</v>
       </c>
       <c r="K52" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.4">
@@ -9207,7 +10919,7 @@
         <v>22</v>
       </c>
       <c r="C55" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D55">
         <v>65</v>
@@ -9231,7 +10943,7 @@
         <v>10</v>
       </c>
       <c r="K55" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.4">
@@ -9309,7 +11021,7 @@
         <v>25</v>
       </c>
       <c r="C59" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D59">
         <v>70</v>
@@ -9336,7 +11048,7 @@
         <v>3</v>
       </c>
       <c r="L59" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.4">
@@ -9347,7 +11059,7 @@
         <v>25</v>
       </c>
       <c r="C60" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D60">
         <v>40</v>
@@ -9385,7 +11097,7 @@
         <v>25</v>
       </c>
       <c r="C62" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D62">
         <v>70</v>
@@ -9412,7 +11124,7 @@
         <v>3</v>
       </c>
       <c r="L62" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.4">
@@ -9423,7 +11135,7 @@
         <v>25</v>
       </c>
       <c r="C63" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D63">
         <v>40</v>
@@ -9461,7 +11173,7 @@
         <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D65">
         <v>70</v>
@@ -9488,7 +11200,7 @@
         <v>3</v>
       </c>
       <c r="L65" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.4">
@@ -9499,7 +11211,7 @@
         <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D66">
         <v>40</v>
@@ -9537,7 +11249,7 @@
         <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D68">
         <v>70</v>
@@ -9564,7 +11276,7 @@
         <v>3</v>
       </c>
       <c r="L68" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.4">
@@ -9575,7 +11287,7 @@
         <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D69">
         <v>40</v>
@@ -9613,7 +11325,7 @@
         <v>25</v>
       </c>
       <c r="C71" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -9640,7 +11352,7 @@
         <v>3</v>
       </c>
       <c r="L71" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.4">
@@ -9651,7 +11363,7 @@
         <v>25</v>
       </c>
       <c r="C72" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D72">
         <v>40</v>
@@ -9689,7 +11401,7 @@
         <v>25</v>
       </c>
       <c r="C74" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D74">
         <v>70</v>
@@ -9716,7 +11428,7 @@
         <v>3</v>
       </c>
       <c r="L74" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.4">
@@ -9727,7 +11439,7 @@
         <v>25</v>
       </c>
       <c r="C75" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D75">
         <v>40</v>
@@ -9765,7 +11477,7 @@
         <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D77">
         <v>70</v>
@@ -9792,7 +11504,7 @@
         <v>3</v>
       </c>
       <c r="L77" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.4">
@@ -9803,7 +11515,7 @@
         <v>25</v>
       </c>
       <c r="C78" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D78">
         <v>40</v>
@@ -9845,7 +11557,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
@@ -9855,7 +11567,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
@@ -9881,12 +11593,12 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A92" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -9903,13 +11615,16 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>404</v>
+        <v>403</v>
+      </c>
+      <c r="H1" t="s">
+        <v>504</v>
       </c>
       <c r="I1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="J1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.4">
@@ -9923,7 +11638,7 @@
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="I2">
         <v>100</v>
@@ -9945,7 +11660,7 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="I3">
         <v>75</v>
@@ -9967,7 +11682,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -9992,7 +11707,7 @@
         <v>180</v>
       </c>
       <c r="H5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -10005,10 +11720,10 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="H6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="I6">
         <v>125</v>
@@ -10021,63 +11736,33 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>486</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>2</v>
+        <v>484</v>
       </c>
       <c r="Z7" s="9"/>
       <c r="AA7" s="9"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>487</v>
-      </c>
-      <c r="P8">
-        <v>2</v>
-      </c>
-      <c r="Q8">
-        <v>2</v>
+        <v>485</v>
       </c>
       <c r="Z8" s="9"/>
       <c r="AA8" s="9"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>488</v>
-      </c>
-      <c r="P9">
-        <v>3</v>
-      </c>
-      <c r="Q9">
-        <v>2</v>
+        <v>486</v>
       </c>
       <c r="Z9" s="9"/>
       <c r="AA9" s="9"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>497</v>
-      </c>
-      <c r="P10">
-        <v>4</v>
-      </c>
-      <c r="Q10">
-        <v>3</v>
+        <v>495</v>
       </c>
       <c r="Z10" s="9"/>
       <c r="AA10" s="9"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="P11">
-        <v>5</v>
-      </c>
-      <c r="Q11">
-        <v>3</v>
-      </c>
       <c r="Z11" s="9"/>
       <c r="AA11" s="9"/>
     </row>
@@ -10088,12 +11773,6 @@
       <c r="B12">
         <v>2</v>
       </c>
-      <c r="P12">
-        <v>6</v>
-      </c>
-      <c r="Q12">
-        <v>3</v>
-      </c>
       <c r="Z12" s="9"/>
       <c r="AA12" s="9"/>
     </row>
@@ -10105,13 +11784,7 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>403</v>
-      </c>
-      <c r="P13">
-        <v>7</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
+        <v>402</v>
       </c>
       <c r="Z13" s="9"/>
       <c r="AA13" s="9"/>
@@ -10121,31 +11794,25 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D14" t="s">
         <v>340</v>
       </c>
       <c r="E14" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G14" t="s">
         <v>357</v>
       </c>
       <c r="H14" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K14" t="s">
-        <v>478</v>
-      </c>
-      <c r="P14">
-        <v>8</v>
-      </c>
-      <c r="Q14">
-        <v>4</v>
+        <v>476</v>
       </c>
       <c r="Z14" s="9"/>
       <c r="AA14" s="9"/>
@@ -10155,16 +11822,10 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D15" t="s">
-        <v>481</v>
-      </c>
-      <c r="P15">
-        <v>9</v>
-      </c>
-      <c r="Q15">
-        <v>4</v>
+        <v>479</v>
       </c>
       <c r="Z15" s="9"/>
       <c r="AA15" s="9"/>
@@ -10174,48 +11835,28 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
+        <v>480</v>
+      </c>
+      <c r="D16" t="s">
         <v>482</v>
       </c>
-      <c r="D16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P16">
-        <v>10</v>
-      </c>
-      <c r="Q16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="P17">
-        <v>11</v>
-      </c>
-      <c r="Q17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
         <v>135</v>
       </c>
-      <c r="P18">
-        <v>12</v>
-      </c>
-      <c r="Q18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B20" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -10241,10 +11882,10 @@
         <v>21</v>
       </c>
       <c r="J22" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>1</v>
       </c>
@@ -10252,7 +11893,7 @@
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D23">
         <v>50</v>
@@ -10276,10 +11917,10 @@
         <v>5</v>
       </c>
       <c r="K23" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>1</v>
       </c>
@@ -10311,15 +11952,15 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B26" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -10350,11 +11991,8 @@
       <c r="K28" t="s">
         <v>183</v>
       </c>
-      <c r="T28" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>1</v>
       </c>
@@ -10362,7 +12000,7 @@
         <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D30">
         <v>60</v>
@@ -10392,14 +12030,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B32" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.4">
@@ -10439,7 +12077,7 @@
         <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D38">
         <v>50</v>
@@ -10463,7 +12101,7 @@
         <v>5</v>
       </c>
       <c r="K38" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.4">
@@ -10498,7 +12136,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.4">
@@ -10509,7 +12147,7 @@
         <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D41">
         <v>50</v>
@@ -10533,7 +12171,7 @@
         <v>5</v>
       </c>
       <c r="K41" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.4">
@@ -10568,7 +12206,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.4">
@@ -10579,7 +12217,7 @@
         <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D44">
         <v>50</v>
@@ -10603,7 +12241,7 @@
         <v>5</v>
       </c>
       <c r="K44" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.4">
@@ -10638,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.4">
@@ -10649,7 +12287,7 @@
         <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D47">
         <v>50</v>
@@ -10673,7 +12311,7 @@
         <v>5</v>
       </c>
       <c r="K47" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.4">
@@ -10708,7 +12346,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.4">
@@ -10719,7 +12357,7 @@
         <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D50">
         <v>50</v>
@@ -10743,7 +12381,7 @@
         <v>5</v>
       </c>
       <c r="K50" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.4">
@@ -10778,7 +12416,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.4">
@@ -10789,7 +12427,7 @@
         <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D53">
         <v>50</v>
@@ -10813,7 +12451,7 @@
         <v>5</v>
       </c>
       <c r="K53" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.4">
@@ -10848,7 +12486,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.4">
@@ -10859,7 +12497,7 @@
         <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D56">
         <v>50</v>
@@ -10883,7 +12521,7 @@
         <v>5</v>
       </c>
       <c r="K56" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.4">
@@ -10918,7 +12556,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.4">
@@ -10966,7 +12604,7 @@
         <v>25</v>
       </c>
       <c r="C61" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -11009,7 +12647,7 @@
         <v>25</v>
       </c>
       <c r="C64" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D64">
         <v>60</v>
@@ -11052,7 +12690,7 @@
         <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D67">
         <v>60</v>
@@ -11095,7 +12733,7 @@
         <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D70">
         <v>60</v>
@@ -11138,7 +12776,7 @@
         <v>25</v>
       </c>
       <c r="C73" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D73">
         <v>60</v>
@@ -11181,7 +12819,7 @@
         <v>25</v>
       </c>
       <c r="C76" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D76">
         <v>60</v>
@@ -11224,7 +12862,7 @@
         <v>25</v>
       </c>
       <c r="C79" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D79">
         <v>60</v>
@@ -11266,7 +12904,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
@@ -11276,7 +12914,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
@@ -11294,7 +12932,7 @@
         <v>39</v>
       </c>
       <c r="B91" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D91" t="s">
         <v>138</v>
@@ -11302,12 +12940,12 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
@@ -11320,678 +12958,3243 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF8D88E9-94CD-49D3-A71A-3DD1767249D5}">
-  <dimension ref="A1:C127"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AF829DA-3810-4F98-BD8D-4E36E3FF81AB}">
+  <dimension ref="A1:AA117"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3">
+        <v>510</v>
+      </c>
+      <c r="H1" t="s">
+        <v>504</v>
+      </c>
+      <c r="I1" t="s">
+        <v>502</v>
+      </c>
+      <c r="J1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>750</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
       </c>
+      <c r="H2" t="s">
+        <v>497</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
+      </c>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
       <c r="B3">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4">
+        <v>1250</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>499</v>
+      </c>
+      <c r="I3">
+        <v>125</v>
+      </c>
+      <c r="J3">
+        <v>125</v>
+      </c>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>500</v>
+      </c>
+      <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" t="s">
+        <v>179</v>
+      </c>
+      <c r="H5" t="s">
+        <v>501</v>
+      </c>
+      <c r="I5">
+        <v>75</v>
+      </c>
+      <c r="J5">
+        <v>75</v>
+      </c>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="H6" t="s">
+        <v>498</v>
+      </c>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>512</v>
+      </c>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>526</v>
+      </c>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>511</v>
+      </c>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>406</v>
+      </c>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>513</v>
+      </c>
+      <c r="D14" t="s">
+        <v>340</v>
+      </c>
+      <c r="E14" t="s">
+        <v>514</v>
+      </c>
+      <c r="G14" t="s">
+        <v>357</v>
+      </c>
+      <c r="H14" t="s">
+        <v>515</v>
+      </c>
+      <c r="J14" t="s">
+        <v>360</v>
+      </c>
+      <c r="K14" t="s">
+        <v>516</v>
+      </c>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>517</v>
+      </c>
+      <c r="D15" t="s">
+        <v>518</v>
+      </c>
+      <c r="Z15" s="9"/>
+      <c r="AA15" s="9"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
+        <v>525</v>
+      </c>
+      <c r="C38" t="s">
+        <v>523</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0.5</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>20</v>
+      </c>
+      <c r="H38">
+        <v>15</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>20</v>
+      </c>
+      <c r="K38" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <v>1</v>
+      </c>
+      <c r="B39" t="s">
+        <v>525</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>1.5</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <v>2</v>
+      </c>
+      <c r="B41" t="s">
+        <v>525</v>
+      </c>
+      <c r="C41" t="s">
+        <v>523</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0.5</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>20</v>
+      </c>
+      <c r="H41">
+        <v>15</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>20</v>
+      </c>
+      <c r="K41" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <v>2</v>
+      </c>
+      <c r="B42" t="s">
+        <v>525</v>
+      </c>
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>1.5</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A44">
         <v>3</v>
       </c>
+      <c r="B44" t="s">
+        <v>525</v>
+      </c>
+      <c r="C44" t="s">
+        <v>523</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0.5</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44">
+        <v>20</v>
+      </c>
+      <c r="H44">
+        <v>15</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>20</v>
+      </c>
+      <c r="K44" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45" t="s">
+        <v>525</v>
+      </c>
+      <c r="C45" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>1.5</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s">
+        <v>525</v>
+      </c>
+      <c r="C47" t="s">
+        <v>523</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0.5</v>
+      </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
+      <c r="G47">
+        <v>20</v>
+      </c>
+      <c r="H47">
+        <v>15</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>20</v>
+      </c>
+      <c r="K47" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48" t="s">
+        <v>525</v>
+      </c>
+      <c r="C48" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>1.5</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A50">
+        <v>5</v>
+      </c>
+      <c r="B50" t="s">
+        <v>525</v>
+      </c>
+      <c r="C50" t="s">
+        <v>523</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0.5</v>
+      </c>
+      <c r="F50">
+        <v>3</v>
+      </c>
+      <c r="G50">
+        <v>20</v>
+      </c>
+      <c r="H50">
+        <v>15</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>20</v>
+      </c>
+      <c r="K50" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A51">
+        <v>5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>525</v>
+      </c>
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>1.5</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A53">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>525</v>
+      </c>
+      <c r="C53" t="s">
+        <v>523</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0.5</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53">
+        <v>20</v>
+      </c>
+      <c r="H53">
+        <v>15</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <v>20</v>
+      </c>
+      <c r="K53" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A54">
+        <v>6</v>
+      </c>
+      <c r="B54" t="s">
+        <v>525</v>
+      </c>
+      <c r="C54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>1.5</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A56">
+        <v>7</v>
+      </c>
+      <c r="B56" t="s">
+        <v>525</v>
+      </c>
+      <c r="C56" t="s">
+        <v>523</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0.5</v>
+      </c>
+      <c r="F56">
+        <v>4</v>
+      </c>
+      <c r="G56">
+        <v>20</v>
+      </c>
+      <c r="H56">
+        <v>15</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56">
+        <v>20</v>
+      </c>
+      <c r="K56" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A57">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>525</v>
+      </c>
+      <c r="C57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>1.5</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>39</v>
+      </c>
+      <c r="B91" t="s">
+        <v>492</v>
+      </c>
+      <c r="D91" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A92" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>10</v>
+      </c>
+      <c r="B93" t="s">
+        <v>517</v>
+      </c>
+      <c r="D93" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>14</v>
+      </c>
+      <c r="B97" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" t="s">
+        <v>16</v>
+      </c>
+      <c r="E97" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" t="s">
+        <v>20</v>
+      </c>
+      <c r="I97" t="s">
+        <v>174</v>
+      </c>
+      <c r="J97" t="s">
+        <v>21</v>
+      </c>
+      <c r="K97" t="s">
+        <v>183</v>
+      </c>
+      <c r="P97" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A98">
+        <v>1</v>
+      </c>
+      <c r="B98" t="s">
+        <v>521</v>
+      </c>
+      <c r="C98" t="s">
+        <v>147</v>
+      </c>
+      <c r="D98">
+        <v>120</v>
+      </c>
+      <c r="E98">
+        <v>0.5</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
+        <v>28</v>
+      </c>
+      <c r="H98">
+        <v>6</v>
+      </c>
+      <c r="I98">
+        <v>3</v>
+      </c>
+      <c r="J98">
+        <v>5</v>
+      </c>
+      <c r="K98">
+        <v>3</v>
+      </c>
+      <c r="L98" t="s">
+        <v>149</v>
+      </c>
+      <c r="P98">
+        <f>(1/E98)*D98</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A99">
+        <v>1</v>
+      </c>
+      <c r="B99" t="s">
+        <v>521</v>
+      </c>
+      <c r="C99" t="s">
+        <v>146</v>
+      </c>
+      <c r="D99">
+        <v>120</v>
+      </c>
+      <c r="E99">
+        <v>0.8</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>28</v>
+      </c>
+      <c r="H99">
+        <v>18</v>
+      </c>
+      <c r="I99">
+        <v>0.5</v>
+      </c>
+      <c r="J99">
+        <v>200</v>
+      </c>
+      <c r="K99">
+        <v>8</v>
+      </c>
+      <c r="L99" t="s">
+        <v>131</v>
+      </c>
+      <c r="P99">
+        <f>(1/E99)*D99</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A101">
+        <v>2</v>
+      </c>
+      <c r="B101" t="s">
+        <v>521</v>
+      </c>
+      <c r="C101" t="s">
+        <v>147</v>
+      </c>
+      <c r="D101">
+        <v>120</v>
+      </c>
+      <c r="E101">
+        <v>0.5</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>28</v>
+      </c>
+      <c r="H101">
+        <v>6</v>
+      </c>
+      <c r="I101">
+        <v>3</v>
+      </c>
+      <c r="J101">
+        <v>5</v>
+      </c>
+      <c r="K101">
+        <v>3</v>
+      </c>
+      <c r="L101" t="s">
+        <v>149</v>
+      </c>
+      <c r="P101">
+        <f>(1/E101)*D101</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A102">
+        <v>2</v>
+      </c>
+      <c r="B102" t="s">
+        <v>521</v>
+      </c>
+      <c r="C102" t="s">
+        <v>146</v>
+      </c>
+      <c r="D102">
+        <v>120</v>
+      </c>
+      <c r="E102">
+        <v>0.8</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102">
+        <v>28</v>
+      </c>
+      <c r="H102">
+        <v>18</v>
+      </c>
+      <c r="I102">
+        <v>0.5</v>
+      </c>
+      <c r="J102">
+        <v>200</v>
+      </c>
+      <c r="K102">
+        <v>8</v>
+      </c>
+      <c r="L102" t="s">
+        <v>131</v>
+      </c>
+      <c r="P102">
+        <f>(1/E102)*D102</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A104">
+        <v>3</v>
+      </c>
+      <c r="B104" t="s">
+        <v>521</v>
+      </c>
+      <c r="C104" t="s">
+        <v>147</v>
+      </c>
+      <c r="D104">
+        <v>120</v>
+      </c>
+      <c r="E104">
+        <v>0.5</v>
+      </c>
+      <c r="F104">
+        <v>2</v>
+      </c>
+      <c r="G104">
+        <v>28</v>
+      </c>
+      <c r="H104">
+        <v>6</v>
+      </c>
+      <c r="I104">
+        <v>3</v>
+      </c>
+      <c r="J104">
+        <v>5</v>
+      </c>
+      <c r="K104">
+        <v>3</v>
+      </c>
+      <c r="L104" t="s">
+        <v>149</v>
+      </c>
+      <c r="P104">
+        <f>(1/E104)*D104</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A105">
+        <v>3</v>
+      </c>
+      <c r="B105" t="s">
+        <v>521</v>
+      </c>
+      <c r="C105" t="s">
+        <v>146</v>
+      </c>
+      <c r="D105">
+        <v>120</v>
+      </c>
+      <c r="E105">
+        <v>0.8</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="G105">
+        <v>28</v>
+      </c>
+      <c r="H105">
+        <v>18</v>
+      </c>
+      <c r="I105">
+        <v>0.5</v>
+      </c>
+      <c r="J105">
+        <v>200</v>
+      </c>
+      <c r="K105">
+        <v>8</v>
+      </c>
+      <c r="L105" t="s">
+        <v>131</v>
+      </c>
+      <c r="P105">
+        <f>(1/E105)*D105</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A107">
+        <v>4</v>
+      </c>
+      <c r="B107" t="s">
+        <v>521</v>
+      </c>
+      <c r="C107" t="s">
+        <v>147</v>
+      </c>
+      <c r="D107">
+        <v>120</v>
+      </c>
+      <c r="E107">
+        <v>0.5</v>
+      </c>
+      <c r="F107">
+        <v>2</v>
+      </c>
+      <c r="G107">
+        <v>28</v>
+      </c>
+      <c r="H107">
+        <v>6</v>
+      </c>
+      <c r="I107">
+        <v>3</v>
+      </c>
+      <c r="J107">
+        <v>5</v>
+      </c>
+      <c r="K107">
+        <v>3</v>
+      </c>
+      <c r="L107" t="s">
+        <v>149</v>
+      </c>
+      <c r="P107">
+        <f>(1/E107)*D107</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A108">
+        <v>4</v>
+      </c>
+      <c r="B108" t="s">
+        <v>521</v>
+      </c>
+      <c r="C108" t="s">
+        <v>146</v>
+      </c>
+      <c r="D108">
+        <v>120</v>
+      </c>
+      <c r="E108">
+        <v>0.8</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="G108">
+        <v>28</v>
+      </c>
+      <c r="H108">
+        <v>18</v>
+      </c>
+      <c r="I108">
+        <v>0.5</v>
+      </c>
+      <c r="J108">
+        <v>200</v>
+      </c>
+      <c r="K108">
+        <v>8</v>
+      </c>
+      <c r="L108" t="s">
+        <v>131</v>
+      </c>
+      <c r="P108">
+        <f>(1/E108)*D108</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A110">
+        <v>5</v>
+      </c>
+      <c r="B110" t="s">
+        <v>521</v>
+      </c>
+      <c r="C110" t="s">
+        <v>147</v>
+      </c>
+      <c r="D110">
+        <v>120</v>
+      </c>
+      <c r="E110">
+        <v>0.5</v>
+      </c>
+      <c r="F110">
+        <v>3</v>
+      </c>
+      <c r="G110">
+        <v>28</v>
+      </c>
+      <c r="H110">
+        <v>6</v>
+      </c>
+      <c r="I110">
+        <v>3</v>
+      </c>
+      <c r="J110">
+        <v>5</v>
+      </c>
+      <c r="K110">
+        <v>3</v>
+      </c>
+      <c r="L110" t="s">
+        <v>149</v>
+      </c>
+      <c r="P110">
+        <f>(1/E110)*D110</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A111">
+        <v>5</v>
+      </c>
+      <c r="B111" t="s">
+        <v>521</v>
+      </c>
+      <c r="C111" t="s">
+        <v>146</v>
+      </c>
+      <c r="D111">
+        <v>120</v>
+      </c>
+      <c r="E111">
+        <v>0.8</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="G111">
+        <v>28</v>
+      </c>
+      <c r="H111">
+        <v>18</v>
+      </c>
+      <c r="I111">
+        <v>0.5</v>
+      </c>
+      <c r="J111">
+        <v>200</v>
+      </c>
+      <c r="K111">
+        <v>8</v>
+      </c>
+      <c r="L111" t="s">
+        <v>131</v>
+      </c>
+      <c r="P111">
+        <f>(1/E111)*D111</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A113">
+        <v>6</v>
+      </c>
+      <c r="B113" t="s">
+        <v>521</v>
+      </c>
+      <c r="C113" t="s">
+        <v>147</v>
+      </c>
+      <c r="D113">
+        <v>120</v>
+      </c>
+      <c r="E113">
+        <v>0.5</v>
+      </c>
+      <c r="F113">
+        <v>3</v>
+      </c>
+      <c r="G113">
+        <v>28</v>
+      </c>
+      <c r="H113">
+        <v>6</v>
+      </c>
+      <c r="I113">
+        <v>3</v>
+      </c>
+      <c r="J113">
+        <v>5</v>
+      </c>
+      <c r="K113">
+        <v>3</v>
+      </c>
+      <c r="L113" t="s">
+        <v>149</v>
+      </c>
+      <c r="P113">
+        <f>(1/E113)*D113</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A114">
+        <v>6</v>
+      </c>
+      <c r="B114" t="s">
+        <v>521</v>
+      </c>
+      <c r="C114" t="s">
+        <v>146</v>
+      </c>
+      <c r="D114">
+        <v>120</v>
+      </c>
+      <c r="E114">
+        <v>0.8</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="G114">
+        <v>28</v>
+      </c>
+      <c r="H114">
+        <v>18</v>
+      </c>
+      <c r="I114">
+        <v>0.5</v>
+      </c>
+      <c r="J114">
+        <v>200</v>
+      </c>
+      <c r="K114">
+        <v>8</v>
+      </c>
+      <c r="L114" t="s">
+        <v>131</v>
+      </c>
+      <c r="P114">
+        <f>(1/E114)*D114</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A116">
+        <v>7</v>
+      </c>
+      <c r="B116" t="s">
+        <v>521</v>
+      </c>
+      <c r="C116" t="s">
+        <v>147</v>
+      </c>
+      <c r="D116">
+        <v>120</v>
+      </c>
+      <c r="E116">
+        <v>0.5</v>
+      </c>
+      <c r="F116">
+        <v>4</v>
+      </c>
+      <c r="G116">
+        <v>28</v>
+      </c>
+      <c r="H116">
+        <v>6</v>
+      </c>
+      <c r="I116">
+        <v>3</v>
+      </c>
+      <c r="J116">
+        <v>5</v>
+      </c>
+      <c r="K116">
+        <v>3</v>
+      </c>
+      <c r="L116" t="s">
+        <v>149</v>
+      </c>
+      <c r="P116">
+        <f>(1/E116)*D116</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A117">
+        <v>7</v>
+      </c>
+      <c r="B117" t="s">
+        <v>521</v>
+      </c>
+      <c r="C117" t="s">
+        <v>146</v>
+      </c>
+      <c r="D117">
+        <v>120</v>
+      </c>
+      <c r="E117">
+        <v>0.8</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117">
+        <v>28</v>
+      </c>
+      <c r="H117">
+        <v>18</v>
+      </c>
+      <c r="I117">
+        <v>0.5</v>
+      </c>
+      <c r="J117">
+        <v>200</v>
+      </c>
+      <c r="K117">
+        <v>8</v>
+      </c>
+      <c r="L117" t="s">
+        <v>131</v>
+      </c>
+      <c r="P117">
+        <f>(1/E117)*D117</f>
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10E32B2B-0112-4B54-A53E-75E91E4C41B1}">
+  <dimension ref="A1:AA96"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>442</v>
+      </c>
+      <c r="H1" t="s">
+        <v>504</v>
+      </c>
+      <c r="I1" t="s">
+        <v>502</v>
+      </c>
+      <c r="J1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1100</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>497</v>
+      </c>
+      <c r="I2">
+        <v>125</v>
+      </c>
+      <c r="J2">
+        <v>125</v>
+      </c>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1100</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>499</v>
+      </c>
+      <c r="I3">
+        <v>75</v>
+      </c>
+      <c r="J3">
+        <v>75</v>
+      </c>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
       <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5">
+      <c r="I4">
+        <v>75</v>
+      </c>
+      <c r="J4">
+        <v>75</v>
+      </c>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5">
+        <v>70</v>
+      </c>
+      <c r="D5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" t="s">
+        <v>506</v>
+      </c>
+      <c r="H5" t="s">
+        <v>501</v>
+      </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="H6" t="s">
+        <v>498</v>
+      </c>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>507</v>
+      </c>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>508</v>
+      </c>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>509</v>
+      </c>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>441</v>
+      </c>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>540</v>
+      </c>
+      <c r="D14" t="s">
+        <v>340</v>
+      </c>
+      <c r="E14" t="s">
+        <v>543</v>
+      </c>
+      <c r="G14" t="s">
+        <v>357</v>
+      </c>
+      <c r="H14" t="s">
+        <v>546</v>
+      </c>
+      <c r="J14" t="s">
+        <v>360</v>
+      </c>
+      <c r="K14" t="s">
+        <v>547</v>
+      </c>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>541</v>
+      </c>
+      <c r="D15" t="s">
+        <v>544</v>
+      </c>
+      <c r="Z15" s="9"/>
+      <c r="AA15" s="9"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>542</v>
+      </c>
+      <c r="D16" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>487</v>
+      </c>
+      <c r="D23">
+        <v>50</v>
+      </c>
+      <c r="E23">
+        <v>0.5</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>20</v>
+      </c>
+      <c r="H23">
+        <v>10</v>
+      </c>
+      <c r="I23">
+        <v>20</v>
+      </c>
+      <c r="J23">
+        <v>5</v>
+      </c>
+      <c r="K23" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0.5</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s">
+        <v>174</v>
+      </c>
+      <c r="J28" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>372</v>
+      </c>
+      <c r="D30">
+        <v>60</v>
+      </c>
+      <c r="E30">
+        <v>0.4</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>30</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>40</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B35" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
+        <v>528</v>
+      </c>
+      <c r="D38">
+        <v>50</v>
+      </c>
+      <c r="E38">
+        <v>0.5</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>30</v>
+      </c>
+      <c r="H38">
+        <v>18</v>
+      </c>
+      <c r="I38">
+        <v>20</v>
+      </c>
+      <c r="J38">
+        <v>5</v>
+      </c>
+      <c r="K38" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <v>1</v>
+      </c>
+      <c r="B39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0.5</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <v>2</v>
+      </c>
+      <c r="B41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
+        <v>528</v>
+      </c>
+      <c r="D41">
+        <v>50</v>
+      </c>
+      <c r="E41">
+        <v>0.5</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>30</v>
+      </c>
+      <c r="H41">
+        <v>18</v>
+      </c>
+      <c r="I41">
+        <v>20</v>
+      </c>
+      <c r="J41">
+        <v>5</v>
+      </c>
+      <c r="K41" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <v>2</v>
+      </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0.5</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" t="s">
+        <v>528</v>
+      </c>
+      <c r="D44">
+        <v>50</v>
+      </c>
+      <c r="E44">
+        <v>0.5</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44">
+        <v>30</v>
+      </c>
+      <c r="H44">
+        <v>18</v>
+      </c>
+      <c r="I44">
+        <v>20</v>
+      </c>
+      <c r="J44">
+        <v>5</v>
+      </c>
+      <c r="K44" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0.5</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A47">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6">
+      <c r="B47" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" t="s">
+        <v>528</v>
+      </c>
+      <c r="D47">
+        <v>50</v>
+      </c>
+      <c r="E47">
+        <v>0.5</v>
+      </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
+      <c r="G47">
+        <v>30</v>
+      </c>
+      <c r="H47">
+        <v>18</v>
+      </c>
+      <c r="I47">
+        <v>20</v>
+      </c>
+      <c r="J47">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7">
+      <c r="K47" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0.5</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A50">
+        <v>5</v>
+      </c>
+      <c r="B50" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" t="s">
+        <v>528</v>
+      </c>
+      <c r="D50">
+        <v>50</v>
+      </c>
+      <c r="E50">
+        <v>0.5</v>
+      </c>
+      <c r="F50">
+        <v>3</v>
+      </c>
+      <c r="G50">
+        <v>30</v>
+      </c>
+      <c r="H50">
+        <v>18</v>
+      </c>
+      <c r="I50">
+        <v>20</v>
+      </c>
+      <c r="J50">
+        <v>5</v>
+      </c>
+      <c r="K50" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A51">
+        <v>5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0.5</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A53">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8">
+      <c r="B53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" t="s">
+        <v>528</v>
+      </c>
+      <c r="D53">
+        <v>50</v>
+      </c>
+      <c r="E53">
+        <v>0.5</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53">
+        <v>30</v>
+      </c>
+      <c r="H53">
+        <v>18</v>
+      </c>
+      <c r="I53">
+        <v>20</v>
+      </c>
+      <c r="J53">
+        <v>5</v>
+      </c>
+      <c r="K53" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A54">
+        <v>6</v>
+      </c>
+      <c r="B54" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0.5</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A56">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9">
+      <c r="B56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" t="s">
+        <v>528</v>
+      </c>
+      <c r="D56">
+        <v>50</v>
+      </c>
+      <c r="E56">
+        <v>0.5</v>
+      </c>
+      <c r="F56">
+        <v>4</v>
+      </c>
+      <c r="G56">
+        <v>30</v>
+      </c>
+      <c r="H56">
+        <v>18</v>
+      </c>
+      <c r="I56">
+        <v>20</v>
+      </c>
+      <c r="J56">
+        <v>5</v>
+      </c>
+      <c r="K56" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A57">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0.5</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s">
+        <v>174</v>
+      </c>
+      <c r="J59" t="s">
+        <v>21</v>
+      </c>
+      <c r="K59" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A60">
+        <v>1</v>
+      </c>
+      <c r="B60" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" t="s">
+        <v>530</v>
+      </c>
+      <c r="D60">
+        <v>10</v>
+      </c>
+      <c r="E60">
+        <v>0.2</v>
+      </c>
+      <c r="F60">
+        <v>4</v>
+      </c>
+      <c r="G60">
+        <v>35</v>
+      </c>
+      <c r="H60">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11">
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>5</v>
+      </c>
+      <c r="K60" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A61">
+        <v>1</v>
+      </c>
+      <c r="B61" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0.5</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A63">
+        <v>2</v>
+      </c>
+      <c r="B63" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" t="s">
+        <v>530</v>
+      </c>
+      <c r="D63">
         <v>10</v>
       </c>
-      <c r="B11">
-        <v>64000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>128000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>256000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="E63">
+        <v>0.2</v>
+      </c>
+      <c r="F63">
+        <v>4</v>
+      </c>
+      <c r="G63">
+        <v>35</v>
+      </c>
+      <c r="H63">
+        <v>8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>5</v>
+      </c>
+      <c r="K63" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A64">
+        <v>2</v>
+      </c>
+      <c r="B64" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0.5</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A66">
+        <v>3</v>
+      </c>
+      <c r="B66" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" t="s">
+        <v>530</v>
+      </c>
+      <c r="D66">
+        <v>10</v>
+      </c>
+      <c r="E66">
+        <v>0.2</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+      <c r="G66">
+        <v>35</v>
+      </c>
+      <c r="H66">
+        <v>8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>5</v>
+      </c>
+      <c r="K66" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A67">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0.5</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A69">
+        <v>4</v>
+      </c>
+      <c r="B69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" t="s">
+        <v>530</v>
+      </c>
+      <c r="D69">
+        <v>10</v>
+      </c>
+      <c r="E69">
+        <v>0.2</v>
+      </c>
+      <c r="F69">
+        <v>5</v>
+      </c>
+      <c r="G69">
+        <v>35</v>
+      </c>
+      <c r="H69">
+        <v>8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>5</v>
+      </c>
+      <c r="K69" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A70">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>22</v>
+      </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0.5</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A72">
+        <v>5</v>
+      </c>
+      <c r="B72" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" t="s">
+        <v>530</v>
+      </c>
+      <c r="D72">
+        <v>10</v>
+      </c>
+      <c r="E72">
+        <v>0.2</v>
+      </c>
+      <c r="F72">
+        <v>6</v>
+      </c>
+      <c r="G72">
+        <v>35</v>
+      </c>
+      <c r="H72">
+        <v>8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>5</v>
+      </c>
+      <c r="K72" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A73">
+        <v>5</v>
+      </c>
+      <c r="B73" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0.5</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A75">
+        <v>6</v>
+      </c>
+      <c r="B75" t="s">
+        <v>22</v>
+      </c>
+      <c r="C75" t="s">
+        <v>530</v>
+      </c>
+      <c r="D75">
+        <v>10</v>
+      </c>
+      <c r="E75">
+        <v>0.2</v>
+      </c>
+      <c r="F75">
+        <v>6</v>
+      </c>
+      <c r="G75">
+        <v>35</v>
+      </c>
+      <c r="H75">
+        <v>8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>5</v>
+      </c>
+      <c r="K75" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A76">
+        <v>6</v>
+      </c>
+      <c r="B76" t="s">
+        <v>22</v>
+      </c>
+      <c r="C76" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0.5</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A78">
+        <v>7</v>
+      </c>
+      <c r="B78" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78" t="s">
+        <v>530</v>
+      </c>
+      <c r="D78">
+        <v>10</v>
+      </c>
+      <c r="E78">
+        <v>0.2</v>
+      </c>
+      <c r="F78">
+        <v>7</v>
+      </c>
+      <c r="G78">
+        <v>35</v>
+      </c>
+      <c r="H78">
+        <v>8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>5</v>
+      </c>
+      <c r="K78" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A79">
+        <v>7</v>
+      </c>
+      <c r="B79" t="s">
+        <v>22</v>
+      </c>
+      <c r="C79" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0.5</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>39</v>
+      </c>
+      <c r="B91" t="s">
+        <v>492</v>
+      </c>
+      <c r="D91" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A92" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A96" s="10"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32FB1326-14F1-42B8-9837-AA6E67B64349}">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>574</v>
+      </c>
+      <c r="B8" t="s">
+        <v>553</v>
+      </c>
+      <c r="C8" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>574</v>
+      </c>
+      <c r="B9" t="s">
+        <v>552</v>
+      </c>
+      <c r="C9" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>574</v>
+      </c>
+      <c r="B10" t="s">
+        <v>554</v>
+      </c>
+      <c r="C10" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>574</v>
+      </c>
+      <c r="B11" t="s">
+        <v>556</v>
+      </c>
+      <c r="C11" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>574</v>
+      </c>
+      <c r="B12" t="s">
+        <v>557</v>
+      </c>
+      <c r="C12" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>223</v>
-      </c>
-      <c r="B15">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+        <v>575</v>
+      </c>
+      <c r="B15" t="s">
+        <v>563</v>
+      </c>
+      <c r="C15" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+        <v>575</v>
+      </c>
+      <c r="B16" t="s">
+        <v>561</v>
+      </c>
+      <c r="C16" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+        <v>575</v>
+      </c>
+      <c r="B17" t="s">
+        <v>562</v>
+      </c>
+      <c r="C17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+        <v>575</v>
+      </c>
+      <c r="B18" t="s">
+        <v>564</v>
+      </c>
+      <c r="C18" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+        <v>575</v>
+      </c>
+      <c r="B19" t="s">
+        <v>571</v>
+      </c>
+      <c r="C19" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+        <v>576</v>
+      </c>
+      <c r="B22" t="s">
+        <v>582</v>
+      </c>
+      <c r="C22" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+        <v>576</v>
+      </c>
+      <c r="B23" t="s">
+        <v>583</v>
+      </c>
+      <c r="C23" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+        <v>576</v>
+      </c>
+      <c r="B24" t="s">
+        <v>584</v>
+      </c>
+      <c r="C24" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+        <v>576</v>
+      </c>
+      <c r="B25" t="s">
+        <v>585</v>
+      </c>
+      <c r="C25" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+        <v>576</v>
+      </c>
+      <c r="B26" t="s">
+        <v>570</v>
+      </c>
+      <c r="C26" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B28" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+        <v>577</v>
+      </c>
+      <c r="B29" t="s">
+        <v>586</v>
+      </c>
+      <c r="C29" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+        <v>577</v>
+      </c>
+      <c r="B30" t="s">
+        <v>587</v>
+      </c>
+      <c r="C30" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+        <v>577</v>
+      </c>
+      <c r="B31" t="s">
+        <v>588</v>
+      </c>
+      <c r="C31" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+        <v>577</v>
+      </c>
+      <c r="B32" t="s">
+        <v>589</v>
+      </c>
+      <c r="C32" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+        <v>577</v>
+      </c>
+      <c r="B33" t="s">
+        <v>590</v>
+      </c>
+      <c r="C33" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>236</v>
-      </c>
-      <c r="B35" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36">
-        <v>0</v>
-      </c>
-      <c r="B36">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37">
-        <v>1</v>
-      </c>
-      <c r="B37">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38">
-        <v>2</v>
-      </c>
-      <c r="B38">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A39">
-        <v>3</v>
-      </c>
-      <c r="B39">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A40">
-        <v>4</v>
-      </c>
-      <c r="B40">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A41">
-        <v>5</v>
-      </c>
-      <c r="B41">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A42">
-        <v>6</v>
-      </c>
-      <c r="B42">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A43">
-        <v>7</v>
-      </c>
-      <c r="B43">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A44">
-        <v>8</v>
-      </c>
-      <c r="B44">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A45">
-        <v>9</v>
-      </c>
-      <c r="B45">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A46">
-        <v>10</v>
-      </c>
-      <c r="B46">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A47">
-        <v>11</v>
-      </c>
-      <c r="B47">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A48">
-        <v>12</v>
-      </c>
-      <c r="B48">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A50" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A52" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A53" t="s">
-        <v>82</v>
-      </c>
-      <c r="B53" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A54" t="s">
-        <v>84</v>
-      </c>
-      <c r="B54" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A56" t="s">
-        <v>73</v>
-      </c>
-      <c r="C56" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A57" t="s">
-        <v>74</v>
-      </c>
-      <c r="C57" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A58" t="s">
-        <v>75</v>
-      </c>
-      <c r="C58" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A60" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A61" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A63" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A64" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A65" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A66" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A67" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A69" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A70" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A72" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A73" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A74" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A75" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A76" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A78" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A79" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A80" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A81" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A82" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A83" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A84" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A86" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A87" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A88" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A89" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A90" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A92" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A94" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A95" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A96" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A97" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A98" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A99" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A100" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A101" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A102" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A104" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A105" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A106" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A107" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A109" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A110" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A111" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A112" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A113" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A115" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A116" t="s">
-        <v>325</v>
-      </c>
-      <c r="B116">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A117" t="s">
-        <v>323</v>
-      </c>
-      <c r="B117">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A118" t="s">
-        <v>324</v>
-      </c>
-      <c r="B118">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A119" t="s">
-        <v>326</v>
-      </c>
-      <c r="B119">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A120" t="s">
-        <v>327</v>
-      </c>
-      <c r="B120">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A122" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A123" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A124" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A125" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A126" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A127" t="s">
-        <v>334</v>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>592</v>
       </c>
     </row>
   </sheetData>
@@ -12000,7 +16203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9CB837D-4EBE-4F79-AFA5-7C29098E884F}">
   <dimension ref="A1:B77"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -12349,6 +16552,497 @@
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>311</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54209E67-297D-476E-A8A4-A10E90F6AA94}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.375" style="13" customWidth="1"/>
+    <col min="6" max="6" width="9" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>452</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -17381,7 +22075,7 @@
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P1" t="s">
         <v>69</v>
@@ -21592,11 +26286,6 @@
         <v>345</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B31" t="s">
-        <v>163</v>
-      </c>
-    </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B32" t="s">
         <v>164</v>
@@ -22737,8 +27426,8 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A91" s="10" t="s">
-        <v>359</v>
+      <c r="A91" s="15" t="s">
+        <v>505</v>
       </c>
     </row>
   </sheetData>

--- a/public/files/DATA/CHR_data.xlsx
+++ b/public/files/DATA/CHR_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583ECDD9-C5FD-41AA-BF8C-37C9821AEBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31860DB5-D496-4B37-B86E-B1AF6A5F2A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="180" windowWidth="26205" windowHeight="14850" firstSheet="2" activeTab="13" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
+    <workbookView xWindow="2520" yWindow="450" windowWidth="26205" windowHeight="14850" firstSheet="4" activeTab="14" xr2:uid="{6231C4C3-18AE-434C-A5BE-7A8D84F4A7B4}"/>
   </bookViews>
   <sheets>
     <sheet name="共通ﾃﾞｰﾀ" sheetId="9" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="009リフィエル" sheetId="18" r:id="rId12"/>
     <sheet name="010プロセル" sheetId="16" r:id="rId13"/>
     <sheet name="MKP" sheetId="19" r:id="rId14"/>
+    <sheet name="行動ﾊﾟﾀｰﾝ" sheetId="20" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2305" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="632">
   <si>
     <t>李乃果</t>
     <rPh sb="0" eb="1">
@@ -8623,22 +8624,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>戦闘中のSP減少を緩和する(10%減少)</t>
-    <rPh sb="0" eb="3">
-      <t>セントウチュウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ゲンショウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カンワ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ゲンショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>MP回復時のSP減少を緩和する　MP1→HP33</t>
     <rPh sb="2" eb="4">
       <t>カイフク</t>
@@ -8665,19 +8650,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>戦闘中のSP減少を緩和する(10%減少)</t>
-    <rPh sb="0" eb="3">
-      <t>セントウチュウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ゲンショウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カンワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>HP回復時のMP減少を10%緩和する</t>
     <rPh sb="2" eb="4">
       <t>カイフク</t>
@@ -8791,6 +8763,209 @@
     </rPh>
     <rPh sb="11" eb="13">
       <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘中のMP減少を緩和する(10%減少)</t>
+    <rPh sb="0" eb="3">
+      <t>セントウチュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンワ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘中のMP減少を緩和する(10%減少)</t>
+    <rPh sb="0" eb="3">
+      <t>セントウチュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本的な配置は前衛</t>
+    <rPh sb="0" eb="3">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゼンエイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本的な配置は後衛</t>
+    <rPh sb="0" eb="3">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前後位置は隊列設定で決められた位置に従う。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンゴ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>タイレツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>シタガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F,M,B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誰も前衛にいないと前衛に出る</t>
+  </si>
+  <si>
+    <t>他のメンバーが1秒以内にレーン移動していたら移動しない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他にメンバーがいて、全メンバーの中で最もHPが低くなると後列に下がる。</t>
+    <rPh sb="0" eb="1">
+      <t>ホカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F,B,M</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前衛にいるとき自分の正面に自分の属性の防御力の高い(属性値100未満)キャラクターが来たらレーンを移動する。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンエイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F,M</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前列にいるとき敵の前列にいるキャラクターが自分の属性の防御力の高い(属性値100未満)キャラクターでなければその正面に移動する。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンレツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランダムで左右どちらかのレーンを確認し、誰もいないとそちらに移動する。</t>
+  </si>
+  <si>
+    <t>M,B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前衛にいるとき、目の前に誰かがいたら左右どちらかのレーンへ移動する。</t>
+  </si>
+  <si>
+    <t>後列から動かない。右端か左端近いほうにレーン移動しようとする。</t>
+  </si>
+  <si>
+    <t>回復型</t>
+    <rPh sb="0" eb="3">
+      <t>カイフクガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>味方の2人以上がHPの5%以上を失っていれば撃つ</t>
+  </si>
+  <si>
+    <t>基本</t>
+    <rPh sb="0" eb="2">
+      <t>キホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※雑魚戦</t>
+  </si>
+  <si>
+    <t>雑魚敵が画面に20匹以上、敵の残り数がまだ半分より多ければ必殺技を撃つ</t>
+  </si>
+  <si>
+    <t>※魔女戦</t>
+  </si>
+  <si>
+    <t>ゲージがたまれば撃つ</t>
+  </si>
+  <si>
+    <t>6秒以内に他のメンバーが必殺技を撃っていたら撃たない。</t>
+  </si>
+  <si>
+    <t>必殺技を撃つときは1/2で前衛中央に向かって移動して撃とうとする。1/2で移動せずそのまま撃つ。</t>
+  </si>
+  <si>
+    <t>必殺技を撃つときは1/2で後衛中央に向かって移動して撃とうとする。1/2で移動せずそのまま撃つ。</t>
+    <rPh sb="13" eb="15">
+      <t>コウエイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回復、補助</t>
+    <rPh sb="0" eb="2">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技を撃つときに発動場所にこだわらず、どこでも撃つ</t>
+    <rPh sb="9" eb="13">
+      <t>ハツドウバショ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -15962,7 +16137,7 @@
         <v>554</v>
       </c>
       <c r="C10" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
@@ -15973,7 +16148,7 @@
         <v>556</v>
       </c>
       <c r="C11" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
@@ -16033,7 +16208,7 @@
         <v>564</v>
       </c>
       <c r="C18" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
@@ -16071,7 +16246,7 @@
         <v>583</v>
       </c>
       <c r="C23" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
@@ -16120,7 +16295,7 @@
         <v>586</v>
       </c>
       <c r="C29" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
@@ -16153,7 +16328,7 @@
         <v>589</v>
       </c>
       <c r="C32" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
@@ -16169,22 +16344,22 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
@@ -16195,6 +16370,167 @@
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>592</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F7E82BA-2162-4D1A-BF6D-A9248D636709}">
+  <dimension ref="B1:D21"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B1" t="s">
+        <v>603</v>
+      </c>
+      <c r="C1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C3" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>608</v>
+      </c>
+      <c r="C4" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>603</v>
+      </c>
+      <c r="C5" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>608</v>
+      </c>
+      <c r="C6" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>612</v>
+      </c>
+      <c r="C7" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>614</v>
+      </c>
+      <c r="C8" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>603</v>
+      </c>
+      <c r="C9" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>617</v>
+      </c>
+      <c r="C11" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>575</v>
+      </c>
+      <c r="C13" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>620</v>
+      </c>
+      <c r="C15" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>622</v>
+      </c>
+      <c r="C16" t="s">
+        <v>623</v>
+      </c>
+      <c r="D16" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
+        <v>622</v>
+      </c>
+      <c r="C17" t="s">
+        <v>625</v>
+      </c>
+      <c r="D17" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>622</v>
+      </c>
+      <c r="C18" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>603</v>
+      </c>
+      <c r="C19" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>575</v>
+      </c>
+      <c r="C20" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>630</v>
+      </c>
+      <c r="C21" t="s">
+        <v>631</v>
       </c>
     </row>
   </sheetData>
